--- a/research/traditional_assets/database/data/ghana/ghana_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/ghana/ghana_farming_agriculture.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1420596840915966</v>
+        <v>0.1417382848813676</v>
       </c>
       <c r="C2">
-        <v>60.12130271393256</v>
+        <v>59.71748622408046</v>
       </c>
       <c r="D2">
-        <v>58.73130271393256</v>
+        <v>58.92805622408046</v>
       </c>
       <c r="E2">
-        <v>-0.157</v>
+        <v>0.4435699999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.6005699999999999</v>
       </c>
       <c r="G2">
         <v>1.39</v>
@@ -1451,28 +1451,28 @@
         <v>5.665</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.030208671</v>
       </c>
       <c r="N2">
-        <v>5.665</v>
+        <v>5.634791329</v>
       </c>
       <c r="O2">
-        <v>1.41625</v>
+        <v>1.40869783225</v>
       </c>
       <c r="P2">
-        <v>4.24875</v>
+        <v>4.22609349675</v>
       </c>
       <c r="Q2">
-        <v>4.25375</v>
+        <v>4.23109349675</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1420596840915966</v>
+        <v>0.1427889241225936</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5931721862945856</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>187.5289382972194</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1417382848813676</v>
+        <v>0.1414168856711386</v>
       </c>
       <c r="C3">
-        <v>59.71748622408046</v>
+        <v>59.31499243831617</v>
       </c>
       <c r="D3">
-        <v>58.92805622408046</v>
+        <v>59.12613243831618</v>
       </c>
       <c r="E3">
-        <v>0.4435699999999999</v>
+        <v>1.04414</v>
       </c>
       <c r="F3">
-        <v>0.6005699999999999</v>
+        <v>1.20114</v>
       </c>
       <c r="G3">
         <v>1.39</v>
@@ -1533,28 +1533,28 @@
         <v>5.665</v>
       </c>
       <c r="M3">
-        <v>0.030208671</v>
+        <v>0.06041734199999999</v>
       </c>
       <c r="N3">
-        <v>5.634791329</v>
+        <v>5.604582658</v>
       </c>
       <c r="O3">
-        <v>1.40869783225</v>
+        <v>1.4011456645</v>
       </c>
       <c r="P3">
-        <v>4.22609349675</v>
+        <v>4.2034369935</v>
       </c>
       <c r="Q3">
-        <v>4.23109349675</v>
+        <v>4.2084369935</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1427889241225936</v>
+        <v>0.1435330466032027</v>
       </c>
       <c r="T3">
-        <v>0.5931721862945856</v>
+        <v>0.5977231467541113</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>187.5289382972194</v>
+        <v>93.76446914860969</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1414168856711386</v>
+        <v>0.1410954864609096</v>
       </c>
       <c r="C4">
-        <v>59.31499243831617</v>
+        <v>58.91383473973054</v>
       </c>
       <c r="D4">
-        <v>59.12613243831618</v>
+        <v>59.32554473973054</v>
       </c>
       <c r="E4">
-        <v>1.04414</v>
+        <v>1.64471</v>
       </c>
       <c r="F4">
-        <v>1.20114</v>
+        <v>1.80171</v>
       </c>
       <c r="G4">
         <v>1.39</v>
@@ -1615,28 +1615,28 @@
         <v>5.665</v>
       </c>
       <c r="M4">
-        <v>0.06041734199999999</v>
+        <v>0.09062601299999998</v>
       </c>
       <c r="N4">
-        <v>5.604582658</v>
+        <v>5.574373987</v>
       </c>
       <c r="O4">
-        <v>1.4011456645</v>
+        <v>1.39359349675</v>
       </c>
       <c r="P4">
-        <v>4.2034369935</v>
+        <v>4.18078049025</v>
       </c>
       <c r="Q4">
-        <v>4.2084369935</v>
+        <v>4.18578049025</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1435330466032027</v>
+        <v>0.1442925118153708</v>
       </c>
       <c r="T4">
-        <v>0.5977231467541113</v>
+        <v>0.6023679414499159</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>93.76446914860969</v>
+        <v>62.50964609907314</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1410954864609096</v>
+        <v>0.1407740872506806</v>
       </c>
       <c r="C5">
-        <v>58.91383473973054</v>
+        <v>58.51402669257169</v>
       </c>
       <c r="D5">
-        <v>59.32554473973054</v>
+        <v>59.52630669257169</v>
       </c>
       <c r="E5">
-        <v>1.64471</v>
+        <v>2.24528</v>
       </c>
       <c r="F5">
-        <v>1.80171</v>
+        <v>2.40228</v>
       </c>
       <c r="G5">
         <v>1.39</v>
@@ -1697,28 +1697,28 @@
         <v>5.665</v>
       </c>
       <c r="M5">
-        <v>0.09062601299999998</v>
+        <v>0.120834684</v>
       </c>
       <c r="N5">
-        <v>5.574373987</v>
+        <v>5.544165316</v>
       </c>
       <c r="O5">
-        <v>1.39359349675</v>
+        <v>1.386041329</v>
       </c>
       <c r="P5">
-        <v>4.18078049025</v>
+        <v>4.158123987</v>
       </c>
       <c r="Q5">
-        <v>4.18578049025</v>
+        <v>4.163123987</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1442925118153708</v>
+        <v>0.145067799219459</v>
       </c>
       <c r="T5">
-        <v>0.6023679414499159</v>
+        <v>0.6071095027018831</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>62.50964609907314</v>
+        <v>46.88223457430485</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1407740872506806</v>
+        <v>0.1404526880404516</v>
       </c>
       <c r="C6">
-        <v>58.51402669257169</v>
+        <v>58.11558204532095</v>
       </c>
       <c r="D6">
-        <v>59.52630669257169</v>
+        <v>59.72843204532095</v>
       </c>
       <c r="E6">
-        <v>2.24528</v>
+        <v>2.84585</v>
       </c>
       <c r="F6">
-        <v>2.40228</v>
+        <v>3.00285</v>
       </c>
       <c r="G6">
         <v>1.39</v>
@@ -1779,28 +1779,28 @@
         <v>5.665</v>
       </c>
       <c r="M6">
-        <v>0.120834684</v>
+        <v>0.151043355</v>
       </c>
       <c r="N6">
-        <v>5.544165316</v>
+        <v>5.513956645</v>
       </c>
       <c r="O6">
-        <v>1.386041329</v>
+        <v>1.37848916125</v>
       </c>
       <c r="P6">
-        <v>4.158123987</v>
+        <v>4.13546748375</v>
       </c>
       <c r="Q6">
-        <v>4.163123987</v>
+        <v>4.14046748375</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.145067799219459</v>
+        <v>0.1458594084636333</v>
       </c>
       <c r="T6">
-        <v>0.6071095027018831</v>
+        <v>0.611950886295997</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>46.88223457430485</v>
+        <v>37.50578765944388</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1404526880404516</v>
+        <v>0.1401312888302227</v>
       </c>
       <c r="C7">
-        <v>58.11558204532095</v>
+        <v>57.71851473383113</v>
       </c>
       <c r="D7">
-        <v>59.72843204532095</v>
+        <v>59.93193473383113</v>
       </c>
       <c r="E7">
-        <v>2.84585</v>
+        <v>3.44642</v>
       </c>
       <c r="F7">
-        <v>3.00285</v>
+        <v>3.60342</v>
       </c>
       <c r="G7">
         <v>1.39</v>
@@ -1861,28 +1861,28 @@
         <v>5.665</v>
       </c>
       <c r="M7">
-        <v>0.151043355</v>
+        <v>0.181252026</v>
       </c>
       <c r="N7">
-        <v>5.513956645</v>
+        <v>5.483747974</v>
       </c>
       <c r="O7">
-        <v>1.37848916125</v>
+        <v>1.3709369935</v>
       </c>
       <c r="P7">
-        <v>4.13546748375</v>
+        <v>4.1128109805</v>
       </c>
       <c r="Q7">
-        <v>4.14046748375</v>
+        <v>4.1178109805</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1458594084636333</v>
+        <v>0.1466678604576837</v>
       </c>
       <c r="T7">
-        <v>0.611950886295997</v>
+        <v>0.6168952780516879</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.50578765944388</v>
+        <v>31.25482304953656</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1401312888302227</v>
+        <v>0.1398098896199937</v>
       </c>
       <c r="C8">
-        <v>57.71851473383113</v>
+        <v>57.32283888452964</v>
       </c>
       <c r="D8">
-        <v>59.93193473383113</v>
+        <v>60.13682888452963</v>
       </c>
       <c r="E8">
-        <v>3.446419999999999</v>
+        <v>4.046989999999999</v>
       </c>
       <c r="F8">
-        <v>3.603419999999999</v>
+        <v>4.203989999999999</v>
       </c>
       <c r="G8">
         <v>1.39</v>
@@ -1943,28 +1943,28 @@
         <v>5.665</v>
       </c>
       <c r="M8">
-        <v>0.181252026</v>
+        <v>0.2114606969999999</v>
       </c>
       <c r="N8">
-        <v>5.483747974</v>
+        <v>5.453539303</v>
       </c>
       <c r="O8">
-        <v>1.3709369935</v>
+        <v>1.36338482575</v>
       </c>
       <c r="P8">
-        <v>4.1128109805</v>
+        <v>4.09015447725</v>
       </c>
       <c r="Q8">
-        <v>4.1178109805</v>
+        <v>4.09515447725</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1466678604576837</v>
+        <v>0.1474936985161222</v>
       </c>
       <c r="T8">
-        <v>0.6168952780516879</v>
+        <v>0.6219460008128773</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.25482304953657</v>
+        <v>26.7898483281742</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1398098896199936</v>
+        <v>0.1394884904097647</v>
       </c>
       <c r="C9">
-        <v>57.32283888452967</v>
+        <v>56.92856881768716</v>
       </c>
       <c r="D9">
-        <v>60.13682888452966</v>
+        <v>60.34312881768716</v>
       </c>
       <c r="E9">
-        <v>4.04699</v>
+        <v>4.647559999999999</v>
       </c>
       <c r="F9">
-        <v>4.20399</v>
+        <v>4.804559999999999</v>
       </c>
       <c r="G9">
         <v>1.39</v>
@@ -2025,28 +2025,28 @@
         <v>5.665</v>
       </c>
       <c r="M9">
-        <v>0.211460697</v>
+        <v>0.241669368</v>
       </c>
       <c r="N9">
-        <v>5.453539303</v>
+        <v>5.423330632</v>
       </c>
       <c r="O9">
-        <v>1.36338482575</v>
+        <v>1.355832658</v>
       </c>
       <c r="P9">
-        <v>4.09015447725</v>
+        <v>4.067497974</v>
       </c>
       <c r="Q9">
-        <v>4.09515447725</v>
+        <v>4.072497974</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1474936985161222</v>
+        <v>0.1483374895758312</v>
       </c>
       <c r="T9">
-        <v>0.6219460008128773</v>
+        <v>0.6271065218949624</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.78984832817419</v>
+        <v>23.44111728715242</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1394884904097647</v>
+        <v>0.1391670911995357</v>
       </c>
       <c r="C10">
-        <v>56.92856881768716</v>
+        <v>56.53571905075414</v>
       </c>
       <c r="D10">
-        <v>60.34312881768716</v>
+        <v>60.55084905075414</v>
       </c>
       <c r="E10">
-        <v>4.647559999999999</v>
+        <v>5.24813</v>
       </c>
       <c r="F10">
-        <v>4.804559999999999</v>
+        <v>5.40513</v>
       </c>
       <c r="G10">
         <v>1.39</v>
@@ -2107,28 +2107,28 @@
         <v>5.665</v>
       </c>
       <c r="M10">
-        <v>0.241669368</v>
+        <v>0.271878039</v>
       </c>
       <c r="N10">
-        <v>5.423330632</v>
+        <v>5.393121961</v>
       </c>
       <c r="O10">
-        <v>1.355832658</v>
+        <v>1.34828049025</v>
       </c>
       <c r="P10">
-        <v>4.067497974</v>
+        <v>4.044841470750001</v>
       </c>
       <c r="Q10">
-        <v>4.072497974</v>
+        <v>4.049841470750001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1483374895758312</v>
+        <v>0.1491998254939952</v>
       </c>
       <c r="T10">
-        <v>0.6271065218949624</v>
+        <v>0.6323804610228073</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.44111728715242</v>
+        <v>20.83654869969104</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1391670911995357</v>
+        <v>0.1388456919893067</v>
       </c>
       <c r="C11">
-        <v>56.53571905075414</v>
+        <v>56.14430430176609</v>
       </c>
       <c r="D11">
-        <v>60.55084905075414</v>
+        <v>60.76000430176609</v>
       </c>
       <c r="E11">
-        <v>5.24813</v>
+        <v>5.848699999999999</v>
       </c>
       <c r="F11">
-        <v>5.40513</v>
+        <v>6.005699999999999</v>
       </c>
       <c r="G11">
         <v>1.39</v>
@@ -2189,28 +2189,28 @@
         <v>5.665</v>
       </c>
       <c r="M11">
-        <v>0.271878039</v>
+        <v>0.3020867099999999</v>
       </c>
       <c r="N11">
-        <v>5.393121961</v>
+        <v>5.36291329</v>
       </c>
       <c r="O11">
-        <v>1.34828049025</v>
+        <v>1.3407283225</v>
       </c>
       <c r="P11">
-        <v>4.044841470750001</v>
+        <v>4.022184967499999</v>
       </c>
       <c r="Q11">
-        <v>4.049841470750001</v>
+        <v>4.027184967499999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1491998254939952</v>
+        <v>0.150081324432563</v>
       </c>
       <c r="T11">
-        <v>0.6323804610228073</v>
+        <v>0.6377715987979379</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.83654869969104</v>
+        <v>18.75289382972194</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1388456919893067</v>
+        <v>0.1385242927790777</v>
       </c>
       <c r="C12">
-        <v>56.14430430176609</v>
+        <v>55.75433949282023</v>
       </c>
       <c r="D12">
-        <v>60.76000430176609</v>
+        <v>60.97060949282023</v>
       </c>
       <c r="E12">
-        <v>5.8487</v>
+        <v>6.449269999999999</v>
       </c>
       <c r="F12">
-        <v>6.0057</v>
+        <v>6.606269999999999</v>
       </c>
       <c r="G12">
         <v>1.39</v>
@@ -2271,28 +2271,28 @@
         <v>5.665</v>
       </c>
       <c r="M12">
-        <v>0.30208671</v>
+        <v>0.3322953809999999</v>
       </c>
       <c r="N12">
-        <v>5.36291329</v>
+        <v>5.332704619</v>
       </c>
       <c r="O12">
-        <v>1.3407283225</v>
+        <v>1.33317615475</v>
       </c>
       <c r="P12">
-        <v>4.022184967499999</v>
+        <v>3.99952846425</v>
       </c>
       <c r="Q12">
-        <v>4.027184967499999</v>
+        <v>4.00452846425</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.150081324432563</v>
+        <v>0.1509826323360424</v>
       </c>
       <c r="T12">
-        <v>0.6377715987979379</v>
+        <v>0.6432838857365545</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.75289382972194</v>
+        <v>17.04808529974722</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1385242927790777</v>
+        <v>0.1382028935688487</v>
       </c>
       <c r="C13">
-        <v>55.75433949282023</v>
+        <v>55.36583975362406</v>
       </c>
       <c r="D13">
-        <v>60.97060949282023</v>
+        <v>61.18267975362406</v>
       </c>
       <c r="E13">
-        <v>6.449269999999999</v>
+        <v>7.049839999999999</v>
       </c>
       <c r="F13">
-        <v>6.606269999999999</v>
+        <v>7.206839999999999</v>
       </c>
       <c r="G13">
         <v>1.39</v>
@@ -2353,28 +2353,28 @@
         <v>5.665</v>
       </c>
       <c r="M13">
-        <v>0.3322953809999999</v>
+        <v>0.3625040519999999</v>
       </c>
       <c r="N13">
-        <v>5.332704619</v>
+        <v>5.302495948</v>
       </c>
       <c r="O13">
-        <v>1.33317615475</v>
+        <v>1.325623987</v>
       </c>
       <c r="P13">
-        <v>3.99952846425</v>
+        <v>3.976871961</v>
       </c>
       <c r="Q13">
-        <v>4.00452846425</v>
+        <v>3.981871961</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1509826323360424</v>
+        <v>0.1519044245100553</v>
       </c>
       <c r="T13">
-        <v>0.6432838857365545</v>
+        <v>0.6489214519237759</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.04808529974722</v>
+        <v>15.62741152476828</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1382028935688487</v>
+        <v>0.1378814943586197</v>
       </c>
       <c r="C14">
-        <v>55.36583975362406</v>
+        <v>54.97882042511865</v>
       </c>
       <c r="D14">
-        <v>61.18267975362406</v>
+        <v>61.39623042511865</v>
       </c>
       <c r="E14">
-        <v>7.049839999999999</v>
+        <v>7.65041</v>
       </c>
       <c r="F14">
-        <v>7.206839999999999</v>
+        <v>7.80741</v>
       </c>
       <c r="G14">
         <v>1.39</v>
@@ -2435,28 +2435,28 @@
         <v>5.665</v>
       </c>
       <c r="M14">
-        <v>0.3625040519999999</v>
+        <v>0.392712723</v>
       </c>
       <c r="N14">
-        <v>5.302495948</v>
+        <v>5.272287277</v>
       </c>
       <c r="O14">
-        <v>1.325623987</v>
+        <v>1.31807181925</v>
       </c>
       <c r="P14">
-        <v>3.976871961</v>
+        <v>3.95421545775</v>
       </c>
       <c r="Q14">
-        <v>3.981871961</v>
+        <v>3.95921545775</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1519044245100553</v>
+        <v>0.1528474073087583</v>
       </c>
       <c r="T14">
-        <v>0.6489214519237759</v>
+        <v>0.6546886173336922</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.62741152476828</v>
+        <v>14.42530294593995</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1378814943586197</v>
+        <v>0.1375600951483907</v>
       </c>
       <c r="C15">
-        <v>54.97882042511865</v>
+        <v>54.59329706317803</v>
       </c>
       <c r="D15">
-        <v>61.39623042511865</v>
+        <v>61.61127706317804</v>
       </c>
       <c r="E15">
-        <v>7.65041</v>
+        <v>8.25098</v>
       </c>
       <c r="F15">
-        <v>7.80741</v>
+        <v>8.40798</v>
       </c>
       <c r="G15">
         <v>1.39</v>
@@ -2517,28 +2517,28 @@
         <v>5.665</v>
       </c>
       <c r="M15">
-        <v>0.392712723</v>
+        <v>0.422921394</v>
       </c>
       <c r="N15">
-        <v>5.272287277</v>
+        <v>5.242078606</v>
       </c>
       <c r="O15">
-        <v>1.31807181925</v>
+        <v>1.3105196515</v>
       </c>
       <c r="P15">
-        <v>3.95421545775</v>
+        <v>3.9315589545</v>
       </c>
       <c r="Q15">
-        <v>3.95921545775</v>
+        <v>3.9365589545</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1528474073087583</v>
+        <v>0.1538123199399892</v>
       </c>
       <c r="T15">
-        <v>0.6546886173336922</v>
+        <v>0.6605899028694204</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.42530294593995</v>
+        <v>13.3949241640871</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1375600951483907</v>
+        <v>0.1374074459381617</v>
       </c>
       <c r="C16">
-        <v>54.59329706317803</v>
+        <v>54.09539243812191</v>
       </c>
       <c r="D16">
-        <v>61.61127706317804</v>
+        <v>61.7139424381219</v>
       </c>
       <c r="E16">
-        <v>8.25098</v>
+        <v>8.851550000000001</v>
       </c>
       <c r="F16">
-        <v>8.40798</v>
+        <v>9.008550000000001</v>
       </c>
       <c r="G16">
         <v>1.39</v>
@@ -2599,45 +2599,45 @@
         <v>5.665</v>
       </c>
       <c r="M16">
-        <v>0.422921394</v>
+        <v>0.4666428900000001</v>
       </c>
       <c r="N16">
-        <v>5.242078606</v>
+        <v>5.19835711</v>
       </c>
       <c r="O16">
-        <v>1.3105196515</v>
+        <v>1.2995892775</v>
       </c>
       <c r="P16">
-        <v>3.9315589545</v>
+        <v>3.8987678325</v>
       </c>
       <c r="Q16">
-        <v>3.9365589545</v>
+        <v>3.9037678325</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1538123199399892</v>
+        <v>0.1547999363978373</v>
       </c>
       <c r="T16">
-        <v>0.6605899028694204</v>
+        <v>0.6666300421824599</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.3949241640871</v>
+        <v>12.13990424240686</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1374074459381617</v>
+        <v>0.1370972967279327</v>
       </c>
       <c r="C17">
-        <v>54.09539243812191</v>
+        <v>53.7044730104093</v>
       </c>
       <c r="D17">
-        <v>61.7139424381219</v>
+        <v>61.9235930104093</v>
       </c>
       <c r="E17">
-        <v>8.85155</v>
+        <v>9.452119999999999</v>
       </c>
       <c r="F17">
-        <v>9.00855</v>
+        <v>9.609119999999999</v>
       </c>
       <c r="G17">
         <v>1.39</v>
@@ -2681,28 +2681,28 @@
         <v>5.665</v>
       </c>
       <c r="M17">
-        <v>0.46664289</v>
+        <v>0.4977524159999999</v>
       </c>
       <c r="N17">
-        <v>5.19835711</v>
+        <v>5.167247584</v>
       </c>
       <c r="O17">
-        <v>1.2995892775</v>
+        <v>1.291811896</v>
       </c>
       <c r="P17">
-        <v>3.8987678325</v>
+        <v>3.875435688</v>
       </c>
       <c r="Q17">
-        <v>3.9037678325</v>
+        <v>3.880435688</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1547999363978373</v>
+        <v>0.1558110675332532</v>
       </c>
       <c r="T17">
-        <v>0.6666300421824599</v>
+        <v>0.6728139943362861</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.13990424240687</v>
+        <v>11.38116022725644</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1370972967279327</v>
+        <v>0.1367871475177038</v>
       </c>
       <c r="C18">
-        <v>53.7044730104093</v>
+        <v>53.31498286059342</v>
       </c>
       <c r="D18">
-        <v>61.9235930104093</v>
+        <v>62.13467286059343</v>
       </c>
       <c r="E18">
-        <v>9.452119999999999</v>
+        <v>10.05269</v>
       </c>
       <c r="F18">
-        <v>9.609119999999999</v>
+        <v>10.20969</v>
       </c>
       <c r="G18">
         <v>1.39</v>
@@ -2763,28 +2763,28 @@
         <v>5.665</v>
       </c>
       <c r="M18">
-        <v>0.4977524159999999</v>
+        <v>0.528861942</v>
       </c>
       <c r="N18">
-        <v>5.167247584</v>
+        <v>5.136138058</v>
       </c>
       <c r="O18">
-        <v>1.291811896</v>
+        <v>1.2840345145</v>
       </c>
       <c r="P18">
-        <v>3.875435688</v>
+        <v>3.8521035435</v>
       </c>
       <c r="Q18">
-        <v>3.880435688</v>
+        <v>3.8571035435</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1558110675332532</v>
+        <v>0.1568465632743419</v>
       </c>
       <c r="T18">
-        <v>0.6728139943362861</v>
+        <v>0.6791469573853852</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.38116022725644</v>
+        <v>10.71168021388841</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1367871475177038</v>
+        <v>0.1364769983074748</v>
       </c>
       <c r="C19">
-        <v>53.31498286059342</v>
+        <v>52.92693665466747</v>
       </c>
       <c r="D19">
-        <v>62.13467286059343</v>
+        <v>62.34719665466747</v>
       </c>
       <c r="E19">
-        <v>10.05269</v>
+        <v>10.65326</v>
       </c>
       <c r="F19">
-        <v>10.20969</v>
+        <v>10.81026</v>
       </c>
       <c r="G19">
         <v>1.39</v>
@@ -2845,28 +2845,28 @@
         <v>5.665</v>
       </c>
       <c r="M19">
-        <v>0.528861942</v>
+        <v>0.559971468</v>
       </c>
       <c r="N19">
-        <v>5.136138058</v>
+        <v>5.105028532</v>
       </c>
       <c r="O19">
-        <v>1.2840345145</v>
+        <v>1.276257133</v>
       </c>
       <c r="P19">
-        <v>3.8521035435</v>
+        <v>3.828771399</v>
       </c>
       <c r="Q19">
-        <v>3.8571035435</v>
+        <v>3.833771399</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1568465632743419</v>
+        <v>0.1579073150091156</v>
       </c>
       <c r="T19">
-        <v>0.6791469573853852</v>
+        <v>0.6856343829478769</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.71168021388841</v>
+        <v>10.11658686867239</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1364769983074748</v>
+        <v>0.1364090990972458</v>
       </c>
       <c r="C20">
-        <v>52.92693665466747</v>
+        <v>52.37308740848822</v>
       </c>
       <c r="D20">
-        <v>62.34719665466747</v>
+        <v>62.39391740848821</v>
       </c>
       <c r="E20">
-        <v>10.65326</v>
+        <v>11.25383</v>
       </c>
       <c r="F20">
-        <v>10.81026</v>
+        <v>11.41083</v>
       </c>
       <c r="G20">
         <v>1.39</v>
@@ -2927,45 +2927,45 @@
         <v>5.665</v>
       </c>
       <c r="M20">
-        <v>0.559971468</v>
+        <v>0.610479405</v>
       </c>
       <c r="N20">
-        <v>5.105028532</v>
+        <v>5.054520595</v>
       </c>
       <c r="O20">
-        <v>1.276257133</v>
+        <v>1.26363014875</v>
       </c>
       <c r="P20">
-        <v>3.828771399</v>
+        <v>3.79089044625</v>
       </c>
       <c r="Q20">
-        <v>3.833771399</v>
+        <v>3.79589044625</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1579073150091156</v>
+        <v>0.1589942581447479</v>
       </c>
       <c r="T20">
-        <v>0.6856343829478769</v>
+        <v>0.6922819918575908</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.11658686867239</v>
+        <v>9.279592323020299</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1364090990972458</v>
+        <v>0.1361116998870168</v>
       </c>
       <c r="C21">
-        <v>52.37308740848822</v>
+        <v>51.97798250086928</v>
       </c>
       <c r="D21">
-        <v>62.39391740848821</v>
+        <v>62.59938250086928</v>
       </c>
       <c r="E21">
-        <v>11.25383</v>
+        <v>11.8544</v>
       </c>
       <c r="F21">
-        <v>11.41083</v>
+        <v>12.0114</v>
       </c>
       <c r="G21">
         <v>1.39</v>
@@ -3009,28 +3009,28 @@
         <v>5.665</v>
       </c>
       <c r="M21">
-        <v>0.610479405</v>
+        <v>0.6426099</v>
       </c>
       <c r="N21">
-        <v>5.054520595</v>
+        <v>5.0223901</v>
       </c>
       <c r="O21">
-        <v>1.26363014875</v>
+        <v>1.255597525</v>
       </c>
       <c r="P21">
-        <v>3.79089044625</v>
+        <v>3.766792575</v>
       </c>
       <c r="Q21">
-        <v>3.79589044625</v>
+        <v>3.771792575</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1589942581447479</v>
+        <v>0.160108374858771</v>
       </c>
       <c r="T21">
-        <v>0.6922819918575908</v>
+        <v>0.6990957909900473</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.279592323020299</v>
+        <v>8.815612706869285</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1361116998870168</v>
+        <v>0.1358143006767878</v>
       </c>
       <c r="C22">
-        <v>51.97798250086928</v>
+        <v>51.58423526988051</v>
       </c>
       <c r="D22">
-        <v>62.59938250086928</v>
+        <v>62.80620526988051</v>
       </c>
       <c r="E22">
-        <v>11.8544</v>
+        <v>12.45497</v>
       </c>
       <c r="F22">
-        <v>12.0114</v>
+        <v>12.61197</v>
       </c>
       <c r="G22">
         <v>1.39</v>
@@ -3091,28 +3091,28 @@
         <v>5.665</v>
       </c>
       <c r="M22">
-        <v>0.6426099</v>
+        <v>0.6747403949999999</v>
       </c>
       <c r="N22">
-        <v>5.0223901</v>
+        <v>4.990259605</v>
       </c>
       <c r="O22">
-        <v>1.255597525</v>
+        <v>1.24756490125</v>
       </c>
       <c r="P22">
-        <v>3.766792575</v>
+        <v>3.74269470375</v>
       </c>
       <c r="Q22">
-        <v>3.771792575</v>
+        <v>3.74769470375</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.160108374858771</v>
+        <v>0.161250697059225</v>
       </c>
       <c r="T22">
-        <v>0.6990957909900473</v>
+        <v>0.7060820913663636</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.815612706869285</v>
+        <v>8.395821625589797</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1358143006767878</v>
+        <v>0.1355169014665588</v>
       </c>
       <c r="C23">
-        <v>51.58423526988051</v>
+        <v>51.19185921705674</v>
       </c>
       <c r="D23">
-        <v>62.80620526988051</v>
+        <v>63.01439921705673</v>
       </c>
       <c r="E23">
-        <v>12.45497</v>
+        <v>13.05554</v>
       </c>
       <c r="F23">
-        <v>12.61197</v>
+        <v>13.21254</v>
       </c>
       <c r="G23">
         <v>1.39</v>
@@ -3173,28 +3173,28 @@
         <v>5.665</v>
       </c>
       <c r="M23">
-        <v>0.6747403949999998</v>
+        <v>0.7068708899999999</v>
       </c>
       <c r="N23">
-        <v>4.990259605</v>
+        <v>4.95812911</v>
       </c>
       <c r="O23">
-        <v>1.24756490125</v>
+        <v>1.2395322775</v>
       </c>
       <c r="P23">
-        <v>3.74269470375</v>
+        <v>3.7185968325</v>
       </c>
       <c r="Q23">
-        <v>3.74769470375</v>
+        <v>3.7235968325</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.161250697059225</v>
+        <v>0.1624223095725113</v>
       </c>
       <c r="T23">
-        <v>0.7060820913663636</v>
+        <v>0.7132475276497648</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.395821625589797</v>
+        <v>8.014193369881168</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1355169014665588</v>
+        <v>0.1352195022563298</v>
       </c>
       <c r="C24">
-        <v>51.19185921705674</v>
+        <v>50.80086802355114</v>
       </c>
       <c r="D24">
-        <v>63.01439921705673</v>
+        <v>63.22397802355114</v>
       </c>
       <c r="E24">
-        <v>13.05554</v>
+        <v>13.65611</v>
       </c>
       <c r="F24">
-        <v>13.21254</v>
+        <v>13.81311</v>
       </c>
       <c r="G24">
         <v>1.39</v>
@@ -3255,28 +3255,28 @@
         <v>5.665</v>
       </c>
       <c r="M24">
-        <v>0.7068708899999999</v>
+        <v>0.739001385</v>
       </c>
       <c r="N24">
-        <v>4.95812911</v>
+        <v>4.925998615</v>
       </c>
       <c r="O24">
-        <v>1.2395322775</v>
+        <v>1.23149965375</v>
       </c>
       <c r="P24">
-        <v>3.7185968325</v>
+        <v>3.69449896125</v>
       </c>
       <c r="Q24">
-        <v>3.7235968325</v>
+        <v>3.69949896125</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1624223095725113</v>
+        <v>0.1636243535796491</v>
       </c>
       <c r="T24">
-        <v>0.7132475276497648</v>
+        <v>0.7205990791613064</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.014193369881168</v>
+        <v>7.665750179886334</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1352195022563298</v>
+        <v>0.1350661030461008</v>
       </c>
       <c r="C25">
-        <v>50.80086802355114</v>
+        <v>50.308945180371</v>
       </c>
       <c r="D25">
-        <v>63.22397802355114</v>
+        <v>63.332625180371</v>
       </c>
       <c r="E25">
-        <v>13.65611</v>
+        <v>14.25668</v>
       </c>
       <c r="F25">
-        <v>13.81311</v>
+        <v>14.41368</v>
       </c>
       <c r="G25">
         <v>1.39</v>
@@ -3337,45 +3337,45 @@
         <v>5.665</v>
       </c>
       <c r="M25">
-        <v>0.739001385</v>
+        <v>0.782662824</v>
       </c>
       <c r="N25">
-        <v>4.925998615</v>
+        <v>4.882337176</v>
       </c>
       <c r="O25">
-        <v>1.23149965375</v>
+        <v>1.220584294</v>
       </c>
       <c r="P25">
-        <v>3.69449896125</v>
+        <v>3.661752882</v>
       </c>
       <c r="Q25">
-        <v>3.69949896125</v>
+        <v>3.666752882</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1636243535796491</v>
+        <v>0.1648580303238169</v>
       </c>
       <c r="T25">
-        <v>0.7205990791613064</v>
+        <v>0.7281440925547308</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.665750179886334</v>
+        <v>7.238110494436874</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1350661030461008</v>
+        <v>0.1347747038358718</v>
       </c>
       <c r="C26">
-        <v>50.308945180371</v>
+        <v>49.91579454973843</v>
       </c>
       <c r="D26">
-        <v>63.332625180371</v>
+        <v>63.54004454973843</v>
       </c>
       <c r="E26">
-        <v>14.25668</v>
+        <v>14.85725</v>
       </c>
       <c r="F26">
-        <v>14.41368</v>
+        <v>15.01425</v>
       </c>
       <c r="G26">
         <v>1.39</v>
@@ -3419,28 +3419,28 @@
         <v>5.665</v>
       </c>
       <c r="M26">
-        <v>0.7826628239999999</v>
+        <v>0.815273775</v>
       </c>
       <c r="N26">
-        <v>4.882337176</v>
+        <v>4.849726225</v>
       </c>
       <c r="O26">
-        <v>1.220584294</v>
+        <v>1.21243155625</v>
       </c>
       <c r="P26">
-        <v>3.661752882</v>
+        <v>3.63729466875</v>
       </c>
       <c r="Q26">
-        <v>3.666752882</v>
+        <v>3.64229466875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1648580303238169</v>
+        <v>0.1661246051144958</v>
       </c>
       <c r="T26">
-        <v>0.7281440925547308</v>
+        <v>0.7358903063053129</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.238110494436875</v>
+        <v>6.948586074659399</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1347747038358718</v>
+        <v>0.1344833046256428</v>
       </c>
       <c r="C27">
-        <v>49.91579454973843</v>
+        <v>49.5240070131104</v>
       </c>
       <c r="D27">
-        <v>63.54004454973843</v>
+        <v>63.74882701311041</v>
       </c>
       <c r="E27">
-        <v>14.85725</v>
+        <v>15.45782</v>
       </c>
       <c r="F27">
-        <v>15.01425</v>
+        <v>15.61482</v>
       </c>
       <c r="G27">
         <v>1.39</v>
@@ -3501,28 +3501,28 @@
         <v>5.665</v>
       </c>
       <c r="M27">
-        <v>0.815273775</v>
+        <v>0.847884726</v>
       </c>
       <c r="N27">
-        <v>4.849726225</v>
+        <v>4.817115274</v>
       </c>
       <c r="O27">
-        <v>1.21243155625</v>
+        <v>1.2042788185</v>
       </c>
       <c r="P27">
-        <v>3.63729466875</v>
+        <v>3.6128364555</v>
       </c>
       <c r="Q27">
-        <v>3.64229466875</v>
+        <v>3.6178364555</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1661246051144958</v>
+        <v>0.1674254116562741</v>
       </c>
       <c r="T27">
-        <v>0.7358903063053129</v>
+        <v>0.7438458771842893</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.948586074659399</v>
+        <v>6.681332764095576</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1344833046256428</v>
+        <v>0.1341919054154138</v>
       </c>
       <c r="C28">
-        <v>49.5240070131104</v>
+        <v>49.13359605151264</v>
       </c>
       <c r="D28">
-        <v>63.74882701311041</v>
+        <v>63.95898605151264</v>
       </c>
       <c r="E28">
-        <v>15.45782</v>
+        <v>16.05839</v>
       </c>
       <c r="F28">
-        <v>15.61482</v>
+        <v>16.21539</v>
       </c>
       <c r="G28">
         <v>1.39</v>
@@ -3583,28 +3583,28 @@
         <v>5.665</v>
       </c>
       <c r="M28">
-        <v>0.847884726</v>
+        <v>0.880495677</v>
       </c>
       <c r="N28">
-        <v>4.817115274</v>
+        <v>4.784504323</v>
       </c>
       <c r="O28">
-        <v>1.2042788185</v>
+        <v>1.19612608075</v>
       </c>
       <c r="P28">
-        <v>3.6128364555</v>
+        <v>3.58837824225</v>
       </c>
       <c r="Q28">
-        <v>3.6178364555</v>
+        <v>3.59337824225</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1674254116562741</v>
+        <v>0.1687618567334436</v>
       </c>
       <c r="T28">
-        <v>0.7438458771842893</v>
+        <v>0.7520194089092651</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.681332764095576</v>
+        <v>6.433875995055</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1341919054154138</v>
+        <v>0.1339005062051848</v>
       </c>
       <c r="C29">
-        <v>49.13359605151264</v>
+        <v>48.74457532432898</v>
       </c>
       <c r="D29">
-        <v>63.95898605151264</v>
+        <v>64.17053532432898</v>
       </c>
       <c r="E29">
-        <v>16.05839</v>
+        <v>16.65896</v>
       </c>
       <c r="F29">
-        <v>16.21539</v>
+        <v>16.81596</v>
       </c>
       <c r="G29">
         <v>1.39</v>
@@ -3665,28 +3665,28 @@
         <v>5.665</v>
       </c>
       <c r="M29">
-        <v>0.880495677</v>
+        <v>0.9131066280000001</v>
       </c>
       <c r="N29">
-        <v>4.784504323</v>
+        <v>4.751893372</v>
       </c>
       <c r="O29">
-        <v>1.19612608075</v>
+        <v>1.187973343</v>
       </c>
       <c r="P29">
-        <v>3.58837824225</v>
+        <v>3.563920029</v>
       </c>
       <c r="Q29">
-        <v>3.59337824225</v>
+        <v>3.568920029</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1687618567334436</v>
+        <v>0.170135425284979</v>
       </c>
       <c r="T29">
-        <v>0.7520194089092651</v>
+        <v>0.7604199831821568</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.433875995055</v>
+        <v>6.204094709517319</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1339005062051848</v>
+        <v>0.1338266069949559</v>
       </c>
       <c r="C30">
-        <v>48.74457532432898</v>
+        <v>48.19787712562096</v>
       </c>
       <c r="D30">
-        <v>64.17053532432898</v>
+        <v>64.22440712562096</v>
       </c>
       <c r="E30">
-        <v>16.65896</v>
+        <v>17.25953</v>
       </c>
       <c r="F30">
-        <v>16.81596</v>
+        <v>17.41653</v>
       </c>
       <c r="G30">
         <v>1.39</v>
@@ -3747,45 +3747,45 @@
         <v>5.665</v>
       </c>
       <c r="M30">
-        <v>0.9131066280000001</v>
+        <v>0.9631341090000001</v>
       </c>
       <c r="N30">
-        <v>4.751893372</v>
+        <v>4.701865891</v>
       </c>
       <c r="O30">
-        <v>1.187973343</v>
+        <v>1.17546647275</v>
       </c>
       <c r="P30">
-        <v>3.563920029</v>
+        <v>3.52639941825</v>
       </c>
       <c r="Q30">
-        <v>3.568920029</v>
+        <v>3.531399418249999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.170135425284979</v>
+        <v>0.1715476859083885</v>
       </c>
       <c r="T30">
-        <v>0.7604199831821568</v>
+        <v>0.7690571933500594</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.204094709517319</v>
+        <v>5.881839244466006</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1338266069949559</v>
+        <v>0.1335427077847268</v>
       </c>
       <c r="C31">
-        <v>48.19787712562096</v>
+        <v>47.80511081575922</v>
       </c>
       <c r="D31">
-        <v>64.22440712562096</v>
+        <v>64.43221081575922</v>
       </c>
       <c r="E31">
-        <v>17.25953</v>
+        <v>17.8601</v>
       </c>
       <c r="F31">
-        <v>17.41653</v>
+        <v>18.0171</v>
       </c>
       <c r="G31">
         <v>1.39</v>
@@ -3829,28 +3829,28 @@
         <v>5.665</v>
       </c>
       <c r="M31">
-        <v>0.963134109</v>
+        <v>0.99634563</v>
       </c>
       <c r="N31">
-        <v>4.701865891</v>
+        <v>4.66865437</v>
       </c>
       <c r="O31">
-        <v>1.17546647275</v>
+        <v>1.1671635925</v>
       </c>
       <c r="P31">
-        <v>3.52639941825</v>
+        <v>3.5014907775</v>
       </c>
       <c r="Q31">
-        <v>3.531399418249999</v>
+        <v>3.5064907775</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1715476859083885</v>
+        <v>0.1730002968353241</v>
       </c>
       <c r="T31">
-        <v>0.7690571933500594</v>
+        <v>0.7779411809513308</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.881839244466006</v>
+        <v>5.68577793631714</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1335427077847268</v>
+        <v>0.1332588085744978</v>
       </c>
       <c r="C32">
-        <v>47.80511081575922</v>
+        <v>47.41369360507857</v>
       </c>
       <c r="D32">
-        <v>64.43221081575922</v>
+        <v>64.64136360507857</v>
       </c>
       <c r="E32">
-        <v>17.8601</v>
+        <v>18.46067</v>
       </c>
       <c r="F32">
-        <v>18.0171</v>
+        <v>18.61767</v>
       </c>
       <c r="G32">
         <v>1.39</v>
@@ -3911,28 +3911,28 @@
         <v>5.665</v>
       </c>
       <c r="M32">
-        <v>0.99634563</v>
+        <v>1.029557151</v>
       </c>
       <c r="N32">
-        <v>4.66865437</v>
+        <v>4.635442849</v>
       </c>
       <c r="O32">
-        <v>1.1671635925</v>
+        <v>1.15886071225</v>
       </c>
       <c r="P32">
-        <v>3.5014907775</v>
+        <v>3.47658213675</v>
       </c>
       <c r="Q32">
-        <v>3.5064907775</v>
+        <v>3.48158213675</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1730002968353241</v>
+        <v>0.1744950124268085</v>
       </c>
       <c r="T32">
-        <v>0.7779411809513308</v>
+        <v>0.7870826754395955</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.68577793631714</v>
+        <v>5.502365744823039</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1332588085744978</v>
+        <v>0.1329749093642689</v>
       </c>
       <c r="C33">
-        <v>47.41369360507857</v>
+        <v>47.02363867425888</v>
       </c>
       <c r="D33">
-        <v>64.64136360507857</v>
+        <v>64.85187867425887</v>
       </c>
       <c r="E33">
-        <v>18.46067</v>
+        <v>19.06124</v>
       </c>
       <c r="F33">
-        <v>18.61767</v>
+        <v>19.21824</v>
       </c>
       <c r="G33">
         <v>1.39</v>
@@ -3993,28 +3993,28 @@
         <v>5.665</v>
       </c>
       <c r="M33">
-        <v>1.029557151</v>
+        <v>1.062768672</v>
       </c>
       <c r="N33">
-        <v>4.635442849</v>
+        <v>4.602231328</v>
       </c>
       <c r="O33">
-        <v>1.15886071225</v>
+        <v>1.150557832</v>
       </c>
       <c r="P33">
-        <v>3.47658213675</v>
+        <v>3.451673496</v>
       </c>
       <c r="Q33">
-        <v>3.48158213675</v>
+        <v>3.456673496</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1744950124268085</v>
+        <v>0.1760336902415719</v>
       </c>
       <c r="T33">
-        <v>0.7870826754395955</v>
+        <v>0.7964930374128093</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.502365744823039</v>
+        <v>5.330416815297318</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1329749093642689</v>
+        <v>0.1326910101540399</v>
       </c>
       <c r="C34">
-        <v>47.02363867425888</v>
+        <v>46.63495937624113</v>
       </c>
       <c r="D34">
-        <v>64.85187867425887</v>
+        <v>65.06376937624113</v>
       </c>
       <c r="E34">
-        <v>19.06124</v>
+        <v>19.66181</v>
       </c>
       <c r="F34">
-        <v>19.21824</v>
+        <v>19.81881</v>
       </c>
       <c r="G34">
         <v>1.39</v>
@@ -4075,28 +4075,28 @@
         <v>5.665</v>
       </c>
       <c r="M34">
-        <v>1.062768672</v>
+        <v>1.095980193</v>
       </c>
       <c r="N34">
-        <v>4.602231328</v>
+        <v>4.569019807</v>
       </c>
       <c r="O34">
-        <v>1.150557832</v>
+        <v>1.14225495175</v>
       </c>
       <c r="P34">
-        <v>3.451673496</v>
+        <v>3.42676485525</v>
       </c>
       <c r="Q34">
-        <v>3.456673496</v>
+        <v>3.43176485525</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1760336902415719</v>
+        <v>0.177618298737373</v>
       </c>
       <c r="T34">
-        <v>0.7964930374128093</v>
+        <v>0.8061843057135817</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.330416815297318</v>
+        <v>5.168889033015581</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1326910101540399</v>
+        <v>0.1324071109438109</v>
       </c>
       <c r="C35">
-        <v>46.63495937624113</v>
+        <v>46.24766923905079</v>
       </c>
       <c r="D35">
-        <v>65.06376937624113</v>
+        <v>65.2770492390508</v>
       </c>
       <c r="E35">
-        <v>19.66181</v>
+        <v>20.26238</v>
       </c>
       <c r="F35">
-        <v>19.81881</v>
+        <v>20.41938</v>
       </c>
       <c r="G35">
         <v>1.39</v>
@@ -4157,28 +4157,28 @@
         <v>5.665</v>
       </c>
       <c r="M35">
-        <v>1.095980193</v>
+        <v>1.129191714</v>
       </c>
       <c r="N35">
-        <v>4.569019807</v>
+        <v>4.535808286</v>
       </c>
       <c r="O35">
-        <v>1.14225495175</v>
+        <v>1.1339520715</v>
       </c>
       <c r="P35">
-        <v>3.42676485525</v>
+        <v>3.4018562145</v>
       </c>
       <c r="Q35">
-        <v>3.43176485525</v>
+        <v>3.4068562145</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.177618298737373</v>
+        <v>0.1792509256724407</v>
       </c>
       <c r="T35">
-        <v>0.8061843057135817</v>
+        <v>0.8161692488113471</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.168889033015581</v>
+        <v>5.016862884985711</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1324071109438109</v>
+        <v>0.1321232117335819</v>
       </c>
       <c r="C36">
-        <v>46.24766923905079</v>
+        <v>45.86178196867674</v>
       </c>
       <c r="D36">
-        <v>65.2770492390508</v>
+        <v>65.49173196867675</v>
       </c>
       <c r="E36">
-        <v>20.26238</v>
+        <v>20.86295</v>
       </c>
       <c r="F36">
-        <v>20.41938</v>
+        <v>21.01995</v>
       </c>
       <c r="G36">
         <v>1.39</v>
@@ -4239,28 +4239,28 @@
         <v>5.665</v>
       </c>
       <c r="M36">
-        <v>1.129191714</v>
+        <v>1.162403235</v>
       </c>
       <c r="N36">
-        <v>4.535808286</v>
+        <v>4.502596765</v>
       </c>
       <c r="O36">
-        <v>1.1339520715</v>
+        <v>1.12564919125</v>
       </c>
       <c r="P36">
-        <v>3.4018562145</v>
+        <v>3.37694757375</v>
       </c>
       <c r="Q36">
-        <v>3.4068562145</v>
+        <v>3.38194757375</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1792509256724407</v>
+        <v>0.1809337872824337</v>
       </c>
       <c r="T36">
-        <v>0.8161692488113471</v>
+        <v>0.8264614209275054</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.016862884985711</v>
+        <v>4.87352394541469</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1321232117335819</v>
+        <v>0.1318393125233529</v>
       </c>
       <c r="C37">
-        <v>45.86178196867674</v>
+        <v>45.4773114520076</v>
       </c>
       <c r="D37">
-        <v>65.49173196867675</v>
+        <v>65.7078314520076</v>
       </c>
       <c r="E37">
-        <v>20.86295</v>
+        <v>21.46352</v>
       </c>
       <c r="F37">
-        <v>21.01995</v>
+        <v>21.62052</v>
       </c>
       <c r="G37">
         <v>1.39</v>
@@ -4321,28 +4321,28 @@
         <v>5.665</v>
       </c>
       <c r="M37">
-        <v>1.162403235</v>
+        <v>1.195614756</v>
       </c>
       <c r="N37">
-        <v>4.502596765</v>
+        <v>4.469385244</v>
       </c>
       <c r="O37">
-        <v>1.12564919125</v>
+        <v>1.117346311</v>
       </c>
       <c r="P37">
-        <v>3.37694757375</v>
+        <v>3.352038933</v>
       </c>
       <c r="Q37">
-        <v>3.38194757375</v>
+        <v>3.357038933</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1809337872824337</v>
+        <v>0.1826692383177389</v>
       </c>
       <c r="T37">
-        <v>0.8264614209275054</v>
+        <v>0.8370752234222935</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.87352394541469</v>
+        <v>4.738148280264283</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1318393125233529</v>
+        <v>0.1315554133131239</v>
       </c>
       <c r="C38">
-        <v>45.4773114520076</v>
+        <v>45.09427175982582</v>
       </c>
       <c r="D38">
-        <v>65.7078314520076</v>
+        <v>65.92536175982582</v>
       </c>
       <c r="E38">
-        <v>21.46352</v>
+        <v>22.06409</v>
       </c>
       <c r="F38">
-        <v>21.62052</v>
+        <v>22.22109</v>
       </c>
       <c r="G38">
         <v>1.39</v>
@@ -4403,28 +4403,28 @@
         <v>5.665</v>
       </c>
       <c r="M38">
-        <v>1.195614756</v>
+        <v>1.228826277</v>
       </c>
       <c r="N38">
-        <v>4.469385244</v>
+        <v>4.436173723</v>
       </c>
       <c r="O38">
-        <v>1.117346311</v>
+        <v>1.10904343075</v>
       </c>
       <c r="P38">
-        <v>3.352038933</v>
+        <v>3.327130292250001</v>
       </c>
       <c r="Q38">
-        <v>3.357038933</v>
+        <v>3.33213029225</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1826692383177389</v>
+        <v>0.1844597830367047</v>
       </c>
       <c r="T38">
-        <v>0.8370752234222935</v>
+        <v>0.8480259720280273</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.738148280264283</v>
+        <v>4.61009021863552</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1315554133131239</v>
+        <v>0.131984014102895</v>
       </c>
       <c r="C39">
-        <v>45.09427175982582</v>
+        <v>44.16584905523413</v>
       </c>
       <c r="D39">
-        <v>65.92536175982582</v>
+        <v>65.59750905523413</v>
       </c>
       <c r="E39">
-        <v>22.06409</v>
+        <v>22.66466</v>
       </c>
       <c r="F39">
-        <v>22.22109</v>
+        <v>22.82166</v>
       </c>
       <c r="G39">
         <v>1.39</v>
@@ -4485,45 +4485,45 @@
         <v>5.665</v>
       </c>
       <c r="M39">
-        <v>1.228826277</v>
+        <v>1.319091948</v>
       </c>
       <c r="N39">
-        <v>4.436173723</v>
+        <v>4.345908052</v>
       </c>
       <c r="O39">
-        <v>1.10904343075</v>
+        <v>1.086477013</v>
       </c>
       <c r="P39">
-        <v>3.327130292250001</v>
+        <v>3.259431039</v>
       </c>
       <c r="Q39">
-        <v>3.33213029225</v>
+        <v>3.264431039</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1844597830367047</v>
+        <v>0.1863080872627338</v>
       </c>
       <c r="T39">
-        <v>0.8480259720280273</v>
+        <v>0.8593299705887848</v>
       </c>
       <c r="U39">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.61009021863552</v>
+        <v>4.294621014546592</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.131984014102895</v>
+        <v>0.1317188648926659</v>
       </c>
       <c r="C40">
-        <v>44.16584905523413</v>
+        <v>43.76771571149949</v>
       </c>
       <c r="D40">
-        <v>65.59750905523413</v>
+        <v>65.79994571149949</v>
       </c>
       <c r="E40">
-        <v>22.66466</v>
+        <v>23.26523</v>
       </c>
       <c r="F40">
-        <v>22.82166</v>
+        <v>23.42223</v>
       </c>
       <c r="G40">
         <v>1.39</v>
@@ -4567,28 +4567,28 @@
         <v>5.665</v>
       </c>
       <c r="M40">
-        <v>1.319091948</v>
+        <v>1.353804894</v>
       </c>
       <c r="N40">
-        <v>4.345908052</v>
+        <v>4.311195106</v>
       </c>
       <c r="O40">
-        <v>1.086477013</v>
+        <v>1.0777987765</v>
       </c>
       <c r="P40">
-        <v>3.259431039</v>
+        <v>3.2333963295</v>
       </c>
       <c r="Q40">
-        <v>3.264431039</v>
+        <v>3.2383963295</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1863080872627338</v>
+        <v>0.1882169916273212</v>
       </c>
       <c r="T40">
-        <v>0.8593299705887848</v>
+        <v>0.8710045920531737</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.294621014546592</v>
+        <v>4.184502526994114</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1317188648926659</v>
+        <v>0.1314537156824369</v>
       </c>
       <c r="C41">
-        <v>43.76771571149949</v>
+        <v>43.37083569154892</v>
       </c>
       <c r="D41">
-        <v>65.79994571149949</v>
+        <v>66.00363569154892</v>
       </c>
       <c r="E41">
-        <v>23.26523</v>
+        <v>23.8658</v>
       </c>
       <c r="F41">
-        <v>23.42223</v>
+        <v>24.0228</v>
       </c>
       <c r="G41">
         <v>1.39</v>
@@ -4649,28 +4649,28 @@
         <v>5.665</v>
       </c>
       <c r="M41">
-        <v>1.353804894</v>
+        <v>1.38851784</v>
       </c>
       <c r="N41">
-        <v>4.311195106</v>
+        <v>4.27648216</v>
       </c>
       <c r="O41">
-        <v>1.0777987765</v>
+        <v>1.06912054</v>
       </c>
       <c r="P41">
-        <v>3.2333963295</v>
+        <v>3.20736162</v>
       </c>
       <c r="Q41">
-        <v>3.2383963295</v>
+        <v>3.21236162</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1882169916273212</v>
+        <v>0.1901895261373949</v>
       </c>
       <c r="T41">
-        <v>0.8710045920531737</v>
+        <v>0.8830683675663755</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.184502526994114</v>
+        <v>4.079889963819262</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1314537156824369</v>
+        <v>0.132264816472208</v>
       </c>
       <c r="C42">
-        <v>43.37083569154892</v>
+        <v>42.15110516798055</v>
       </c>
       <c r="D42">
-        <v>66.00363569154892</v>
+        <v>65.38447516798055</v>
       </c>
       <c r="E42">
-        <v>23.8658</v>
+        <v>24.46637</v>
       </c>
       <c r="F42">
-        <v>24.0228</v>
+        <v>24.62337</v>
       </c>
       <c r="G42">
         <v>1.39</v>
@@ -4731,45 +4731,45 @@
         <v>5.665</v>
       </c>
       <c r="M42">
-        <v>1.38851784</v>
+        <v>1.509412581</v>
       </c>
       <c r="N42">
-        <v>4.27648216</v>
+        <v>4.155587419</v>
       </c>
       <c r="O42">
-        <v>1.06912054</v>
+        <v>1.03889685475</v>
       </c>
       <c r="P42">
-        <v>3.20736162</v>
+        <v>3.11669056425</v>
       </c>
       <c r="Q42">
-        <v>3.21236162</v>
+        <v>3.12169056425</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1901895261373949</v>
+        <v>0.1922289262240813</v>
       </c>
       <c r="T42">
-        <v>0.8830683675663755</v>
+        <v>0.8955410846223979</v>
       </c>
       <c r="U42">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.079889963819262</v>
+        <v>3.753115663211767</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.132264816472208</v>
+        <v>0.132025917261979</v>
       </c>
       <c r="C43">
-        <v>42.15110516798055</v>
+        <v>41.7316906717418</v>
       </c>
       <c r="D43">
-        <v>65.38447516798055</v>
+        <v>65.5656306717418</v>
       </c>
       <c r="E43">
-        <v>24.46637</v>
+        <v>25.06694</v>
       </c>
       <c r="F43">
-        <v>24.62337</v>
+        <v>25.22394</v>
       </c>
       <c r="G43">
         <v>1.39</v>
@@ -4813,28 +4813,28 @@
         <v>5.665</v>
       </c>
       <c r="M43">
-        <v>1.509412581</v>
+        <v>1.546227522</v>
       </c>
       <c r="N43">
-        <v>4.155587419</v>
+        <v>4.118772478</v>
       </c>
       <c r="O43">
-        <v>1.03889685475</v>
+        <v>1.0296931195</v>
       </c>
       <c r="P43">
-        <v>3.11669056425</v>
+        <v>3.0890793585</v>
       </c>
       <c r="Q43">
-        <v>3.12169056425</v>
+        <v>3.0940793585</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1922289262240813</v>
+        <v>0.1943386504516879</v>
       </c>
       <c r="T43">
-        <v>0.8955410846223979</v>
+        <v>0.908443895370007</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.753115663211767</v>
+        <v>3.66375576646863</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.132025917261979</v>
+        <v>0.13178701805175</v>
       </c>
       <c r="C44">
-        <v>41.73169067174177</v>
+        <v>41.31328279040276</v>
       </c>
       <c r="D44">
-        <v>65.56563067174177</v>
+        <v>65.74779279040276</v>
       </c>
       <c r="E44">
-        <v>25.06694</v>
+        <v>25.66751</v>
       </c>
       <c r="F44">
-        <v>25.22394</v>
+        <v>25.82451</v>
       </c>
       <c r="G44">
         <v>1.39</v>
@@ -4895,28 +4895,28 @@
         <v>5.665</v>
       </c>
       <c r="M44">
-        <v>1.546227522</v>
+        <v>1.583042463</v>
       </c>
       <c r="N44">
-        <v>4.118772478</v>
+        <v>4.081957537</v>
       </c>
       <c r="O44">
-        <v>1.0296931195</v>
+        <v>1.02048938425</v>
       </c>
       <c r="P44">
-        <v>3.0890793585</v>
+        <v>3.06146815275</v>
       </c>
       <c r="Q44">
-        <v>3.0940793585</v>
+        <v>3.06646815275</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1943386504516879</v>
+        <v>0.1965224000907894</v>
       </c>
       <c r="T44">
-        <v>0.908443895370007</v>
+        <v>0.9217994363192866</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.66375576646863</v>
+        <v>3.578552143992615</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.13178701805175</v>
+        <v>0.132472118841521</v>
       </c>
       <c r="C45">
-        <v>41.31328279040276</v>
+        <v>40.19300858369277</v>
       </c>
       <c r="D45">
-        <v>65.74779279040276</v>
+        <v>65.22808858369277</v>
       </c>
       <c r="E45">
-        <v>25.66751</v>
+        <v>26.26808</v>
       </c>
       <c r="F45">
-        <v>25.82451</v>
+        <v>26.42508</v>
       </c>
       <c r="G45">
         <v>1.39</v>
@@ -4977,45 +4977,45 @@
         <v>5.665</v>
       </c>
       <c r="M45">
-        <v>1.583042463</v>
+        <v>1.693847628</v>
       </c>
       <c r="N45">
-        <v>4.081957537</v>
+        <v>3.971152372</v>
       </c>
       <c r="O45">
-        <v>1.02048938425</v>
+        <v>0.992788093</v>
       </c>
       <c r="P45">
-        <v>3.06146815275</v>
+        <v>2.978364279</v>
       </c>
       <c r="Q45">
-        <v>3.06646815275</v>
+        <v>2.983364279</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1965224000907894</v>
+        <v>0.1987841407884303</v>
       </c>
       <c r="T45">
-        <v>0.9217994363192866</v>
+        <v>0.935631960873898</v>
       </c>
       <c r="U45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.578552143992615</v>
+        <v>3.344456671518272</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.132472118841521</v>
+        <v>0.132254219631292</v>
       </c>
       <c r="C46">
-        <v>40.19300858369277</v>
+        <v>39.75683945443973</v>
       </c>
       <c r="D46">
-        <v>65.22808858369277</v>
+        <v>65.39248945443973</v>
       </c>
       <c r="E46">
-        <v>26.26808</v>
+        <v>26.86865</v>
       </c>
       <c r="F46">
-        <v>26.42508</v>
+        <v>27.02565</v>
       </c>
       <c r="G46">
         <v>1.39</v>
@@ -5059,28 +5059,28 @@
         <v>5.665</v>
       </c>
       <c r="M46">
-        <v>1.693847628</v>
+        <v>1.732344165</v>
       </c>
       <c r="N46">
-        <v>3.971152372</v>
+        <v>3.932655835</v>
       </c>
       <c r="O46">
-        <v>0.992788093</v>
+        <v>0.9831639587500001</v>
       </c>
       <c r="P46">
-        <v>2.978364279</v>
+        <v>2.94949187625</v>
       </c>
       <c r="Q46">
-        <v>2.983364279</v>
+        <v>2.95449187625</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1987841407884303</v>
+        <v>0.2011281266023491</v>
       </c>
       <c r="T46">
-        <v>0.935631960873898</v>
+        <v>0.9499674863214039</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.344456671518272</v>
+        <v>3.270135412151199</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.132254219631292</v>
+        <v>0.132036320421063</v>
       </c>
       <c r="C47">
-        <v>39.75683945443973</v>
+        <v>39.32150113104022</v>
       </c>
       <c r="D47">
-        <v>65.39248945443973</v>
+        <v>65.55772113104022</v>
       </c>
       <c r="E47">
-        <v>26.86865</v>
+        <v>27.46922</v>
       </c>
       <c r="F47">
-        <v>27.02565</v>
+        <v>27.62622</v>
       </c>
       <c r="G47">
         <v>1.39</v>
@@ -5141,28 +5141,28 @@
         <v>5.665</v>
       </c>
       <c r="M47">
-        <v>1.732344165</v>
+        <v>1.770840702</v>
       </c>
       <c r="N47">
-        <v>3.932655835</v>
+        <v>3.894159298</v>
       </c>
       <c r="O47">
-        <v>0.9831639587500001</v>
+        <v>0.9735398245</v>
       </c>
       <c r="P47">
-        <v>2.94949187625</v>
+        <v>2.9206194735</v>
       </c>
       <c r="Q47">
-        <v>2.95449187625</v>
+        <v>2.9256194735</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2011281266023491</v>
+        <v>0.2035589267056722</v>
       </c>
       <c r="T47">
-        <v>0.9499674863214039</v>
+        <v>0.9648339571558547</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.270135412151199</v>
+        <v>3.199045511887042</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.132036320421063</v>
+        <v>0.131818421210834</v>
       </c>
       <c r="C48">
-        <v>39.32150113104022</v>
+        <v>38.88699992720952</v>
       </c>
       <c r="D48">
-        <v>65.55772113104022</v>
+        <v>65.72378992720952</v>
       </c>
       <c r="E48">
-        <v>27.46922</v>
+        <v>28.06979</v>
       </c>
       <c r="F48">
-        <v>27.62622</v>
+        <v>28.22679</v>
       </c>
       <c r="G48">
         <v>1.39</v>
@@ -5223,28 +5223,28 @@
         <v>5.665</v>
       </c>
       <c r="M48">
-        <v>1.770840702</v>
+        <v>1.809337239</v>
       </c>
       <c r="N48">
-        <v>3.894159298</v>
+        <v>3.855662761</v>
       </c>
       <c r="O48">
-        <v>0.9735398245</v>
+        <v>0.9639156902499999</v>
       </c>
       <c r="P48">
-        <v>2.9206194735</v>
+        <v>2.89174707075</v>
       </c>
       <c r="Q48">
-        <v>2.9256194735</v>
+        <v>2.89674707075</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2035589267056722</v>
+        <v>0.2060814551147812</v>
       </c>
       <c r="T48">
-        <v>0.9648339571558547</v>
+        <v>0.9802614268897187</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.199045511887042</v>
+        <v>3.130980713761786</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.131818421210834</v>
+        <v>0.131600522000605</v>
       </c>
       <c r="C49">
-        <v>38.88699992720952</v>
+        <v>38.45334222080017</v>
       </c>
       <c r="D49">
-        <v>65.72378992720952</v>
+        <v>65.89070222080016</v>
       </c>
       <c r="E49">
-        <v>28.06979</v>
+        <v>28.67036</v>
       </c>
       <c r="F49">
-        <v>28.22679</v>
+        <v>28.82736</v>
       </c>
       <c r="G49">
         <v>1.39</v>
@@ -5305,28 +5305,28 @@
         <v>5.665</v>
       </c>
       <c r="M49">
-        <v>1.809337239</v>
+        <v>1.847833776</v>
       </c>
       <c r="N49">
-        <v>3.855662761</v>
+        <v>3.817166224</v>
       </c>
       <c r="O49">
-        <v>0.9639156902499999</v>
+        <v>0.954291556</v>
       </c>
       <c r="P49">
-        <v>2.89174707075</v>
+        <v>2.862874668</v>
       </c>
       <c r="Q49">
-        <v>2.89674707075</v>
+        <v>2.867874668</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2060814551147812</v>
+        <v>0.2087010038473173</v>
       </c>
       <c r="T49">
-        <v>0.9802614268897187</v>
+        <v>0.996282260844116</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.130980713761786</v>
+        <v>3.065751948891749</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.131600522000605</v>
+        <v>0.131382622790376</v>
       </c>
       <c r="C50">
-        <v>38.45334222080017</v>
+        <v>38.02053445461853</v>
       </c>
       <c r="D50">
-        <v>65.89070222080016</v>
+        <v>66.05846445461853</v>
       </c>
       <c r="E50">
-        <v>28.67036</v>
+        <v>29.27093</v>
       </c>
       <c r="F50">
-        <v>28.82736</v>
+        <v>29.42793</v>
       </c>
       <c r="G50">
         <v>1.39</v>
@@ -5387,28 +5387,28 @@
         <v>5.665</v>
       </c>
       <c r="M50">
-        <v>1.847833776</v>
+        <v>1.886330313</v>
       </c>
       <c r="N50">
-        <v>3.817166224</v>
+        <v>3.778669687</v>
       </c>
       <c r="O50">
-        <v>0.954291556</v>
+        <v>0.94466742175</v>
       </c>
       <c r="P50">
-        <v>2.862874668</v>
+        <v>2.83400226525</v>
       </c>
       <c r="Q50">
-        <v>2.867874668</v>
+        <v>2.83900226525</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2087010038473173</v>
+        <v>0.2114232799811294</v>
       </c>
       <c r="T50">
-        <v>0.996282260844116</v>
+        <v>1.012931362796725</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.065751948891749</v>
+        <v>3.003185582587836</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.131382622790376</v>
+        <v>0.134089723580147</v>
       </c>
       <c r="C51">
-        <v>38.02053445461853</v>
+        <v>35.39450878384812</v>
       </c>
       <c r="D51">
-        <v>66.05846445461853</v>
+        <v>64.03300878384812</v>
       </c>
       <c r="E51">
-        <v>29.27093</v>
+        <v>29.8715</v>
       </c>
       <c r="F51">
-        <v>29.42793</v>
+        <v>30.0285</v>
       </c>
       <c r="G51">
         <v>1.39</v>
@@ -5469,45 +5469,45 @@
         <v>5.665</v>
       </c>
       <c r="M51">
-        <v>1.886330313</v>
+        <v>2.15904915</v>
       </c>
       <c r="N51">
-        <v>3.778669687</v>
+        <v>3.50595085</v>
       </c>
       <c r="O51">
-        <v>0.94466742175</v>
+        <v>0.8764877125</v>
       </c>
       <c r="P51">
-        <v>2.83400226525</v>
+        <v>2.6294631375</v>
       </c>
       <c r="Q51">
-        <v>2.83900226525</v>
+        <v>2.6344631375</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2114232799811294</v>
+        <v>0.214254447160294</v>
       </c>
       <c r="T51">
-        <v>1.012931362796725</v>
+        <v>1.030246428827438</v>
       </c>
       <c r="U51">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.003185582587836</v>
+        <v>2.623840221516032</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.134089723580147</v>
+        <v>0.133930324369918</v>
       </c>
       <c r="C52">
-        <v>35.39450878384812</v>
+        <v>34.90975375561528</v>
       </c>
       <c r="D52">
-        <v>64.03300878384812</v>
+        <v>64.14882375561528</v>
       </c>
       <c r="E52">
-        <v>29.8715</v>
+        <v>30.47207</v>
       </c>
       <c r="F52">
-        <v>30.0285</v>
+        <v>30.62907</v>
       </c>
       <c r="G52">
         <v>1.39</v>
@@ -5551,28 +5551,28 @@
         <v>5.665</v>
       </c>
       <c r="M52">
-        <v>2.15904915</v>
+        <v>2.202230133</v>
       </c>
       <c r="N52">
-        <v>3.50595085</v>
+        <v>3.462769867</v>
       </c>
       <c r="O52">
-        <v>0.8764877125</v>
+        <v>0.86569246675</v>
       </c>
       <c r="P52">
-        <v>2.6294631375</v>
+        <v>2.59707740025</v>
       </c>
       <c r="Q52">
-        <v>2.6344631375</v>
+        <v>2.60207740025</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.214254447160294</v>
+        <v>0.2172011721835062</v>
       </c>
       <c r="T52">
-        <v>1.030246428827438</v>
+        <v>1.04826823224716</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.623840221516032</v>
+        <v>2.572392374035325</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.133930324369918</v>
+        <v>0.1337709251596891</v>
       </c>
       <c r="C53">
-        <v>34.90975375561528</v>
+        <v>34.42541843002846</v>
       </c>
       <c r="D53">
-        <v>64.14882375561528</v>
+        <v>64.26505843002846</v>
       </c>
       <c r="E53">
-        <v>30.47207</v>
+        <v>31.07264</v>
       </c>
       <c r="F53">
-        <v>30.62907</v>
+        <v>31.22964</v>
       </c>
       <c r="G53">
         <v>1.39</v>
@@ -5633,28 +5633,28 @@
         <v>5.665</v>
       </c>
       <c r="M53">
-        <v>2.202230133</v>
+        <v>2.245411116</v>
       </c>
       <c r="N53">
-        <v>3.462769867</v>
+        <v>3.419588884</v>
       </c>
       <c r="O53">
-        <v>0.86569246675</v>
+        <v>0.854897221</v>
       </c>
       <c r="P53">
-        <v>2.59707740025</v>
+        <v>2.564691663</v>
       </c>
       <c r="Q53">
-        <v>2.60207740025</v>
+        <v>2.569691663</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2172011721835062</v>
+        <v>0.2202706774160189</v>
       </c>
       <c r="T53">
-        <v>1.04826823224716</v>
+        <v>1.067040944142704</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.572392374035325</v>
+        <v>2.522923289919261</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1337709251596891</v>
+        <v>0.1351617759494601</v>
       </c>
       <c r="C54">
-        <v>34.42541843002846</v>
+        <v>32.82460972256773</v>
       </c>
       <c r="D54">
-        <v>64.26505843002846</v>
+        <v>63.26481972256773</v>
       </c>
       <c r="E54">
-        <v>31.07264</v>
+        <v>31.67321</v>
       </c>
       <c r="F54">
-        <v>31.22964</v>
+        <v>31.83021</v>
       </c>
       <c r="G54">
         <v>1.39</v>
@@ -5715,45 +5715,45 @@
         <v>5.665</v>
       </c>
       <c r="M54">
-        <v>2.245411116</v>
+        <v>2.412729918</v>
       </c>
       <c r="N54">
-        <v>3.419588884</v>
+        <v>3.252270082</v>
       </c>
       <c r="O54">
-        <v>0.854897221</v>
+        <v>0.8130675205</v>
       </c>
       <c r="P54">
-        <v>2.564691663</v>
+        <v>2.4392025615</v>
       </c>
       <c r="Q54">
-        <v>2.569691663</v>
+        <v>2.4442025615</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2202706774160189</v>
+        <v>0.2234707998924682</v>
       </c>
       <c r="T54">
-        <v>1.067040944142704</v>
+        <v>1.086612494842313</v>
       </c>
       <c r="U54">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.522923289919261</v>
+        <v>2.347962761076849</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1351617759494601</v>
+        <v>0.1350316267392311</v>
       </c>
       <c r="C55">
-        <v>32.82460972256773</v>
+        <v>32.31631492389553</v>
       </c>
       <c r="D55">
-        <v>63.26481972256773</v>
+        <v>63.35709492389553</v>
       </c>
       <c r="E55">
-        <v>31.67321</v>
+        <v>32.27378</v>
       </c>
       <c r="F55">
-        <v>31.83021</v>
+        <v>32.43078</v>
       </c>
       <c r="G55">
         <v>1.39</v>
@@ -5797,28 +5797,28 @@
         <v>5.665</v>
       </c>
       <c r="M55">
-        <v>2.412729918</v>
+        <v>2.458253124</v>
       </c>
       <c r="N55">
-        <v>3.252270082</v>
+        <v>3.206746876</v>
       </c>
       <c r="O55">
-        <v>0.8130675205</v>
+        <v>0.801686719</v>
       </c>
       <c r="P55">
-        <v>2.4392025615</v>
+        <v>2.405060157</v>
       </c>
       <c r="Q55">
-        <v>2.4442025615</v>
+        <v>2.410060157</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2234707998924682</v>
+        <v>0.2268100581287632</v>
       </c>
       <c r="T55">
-        <v>1.086612494842313</v>
+        <v>1.107034982528862</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.347962761076849</v>
+        <v>2.304481969205056</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1350316267392311</v>
+        <v>0.1349014775290021</v>
       </c>
       <c r="C56">
-        <v>32.31631492389553</v>
+        <v>31.80828969526665</v>
       </c>
       <c r="D56">
-        <v>63.35709492389553</v>
+        <v>63.44963969526665</v>
       </c>
       <c r="E56">
-        <v>32.27378</v>
+        <v>32.87435000000001</v>
       </c>
       <c r="F56">
-        <v>32.43078</v>
+        <v>33.03135</v>
       </c>
       <c r="G56">
         <v>1.39</v>
@@ -5879,28 +5879,28 @@
         <v>5.665</v>
       </c>
       <c r="M56">
-        <v>2.458253124</v>
+        <v>2.50377633</v>
       </c>
       <c r="N56">
-        <v>3.206746876</v>
+        <v>3.16122367</v>
       </c>
       <c r="O56">
-        <v>0.801686719</v>
+        <v>0.7903059174999999</v>
       </c>
       <c r="P56">
-        <v>2.405060157</v>
+        <v>2.3709177525</v>
       </c>
       <c r="Q56">
-        <v>2.410060157</v>
+        <v>2.375917752499999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2268100581287632</v>
+        <v>0.2302977278422269</v>
       </c>
       <c r="T56">
-        <v>1.107034982528862</v>
+        <v>1.128365136334813</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.304481969205056</v>
+        <v>2.262582297037691</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1349014775290021</v>
+        <v>0.1347713283187731</v>
       </c>
       <c r="C57">
-        <v>31.80828969526665</v>
+        <v>31.30053521967991</v>
       </c>
       <c r="D57">
-        <v>63.44963969526665</v>
+        <v>63.54245521967991</v>
       </c>
       <c r="E57">
-        <v>32.87435000000001</v>
+        <v>33.47492</v>
       </c>
       <c r="F57">
-        <v>33.03135</v>
+        <v>33.63192</v>
       </c>
       <c r="G57">
         <v>1.39</v>
@@ -5961,28 +5961,28 @@
         <v>5.665</v>
       </c>
       <c r="M57">
-        <v>2.50377633</v>
+        <v>2.549299536</v>
       </c>
       <c r="N57">
-        <v>3.16122367</v>
+        <v>3.115700464</v>
       </c>
       <c r="O57">
-        <v>0.7903059174999999</v>
+        <v>0.7789251159999999</v>
       </c>
       <c r="P57">
-        <v>2.3709177525</v>
+        <v>2.336775348</v>
       </c>
       <c r="Q57">
-        <v>2.375917752499999</v>
+        <v>2.341775348</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2302977278422269</v>
+        <v>0.2339439279972116</v>
       </c>
       <c r="T57">
-        <v>1.128365136334813</v>
+        <v>1.150664842586489</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.262582297037691</v>
+        <v>2.222179041733447</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1347713283187731</v>
+        <v>0.1346411791085441</v>
       </c>
       <c r="C58">
-        <v>31.30053521967991</v>
+        <v>30.79305268706649</v>
       </c>
       <c r="D58">
-        <v>63.54245521967991</v>
+        <v>63.6355426870665</v>
       </c>
       <c r="E58">
-        <v>33.47492</v>
+        <v>34.07549</v>
       </c>
       <c r="F58">
-        <v>33.63192</v>
+        <v>34.23249</v>
       </c>
       <c r="G58">
         <v>1.39</v>
@@ -6043,28 +6043,28 @@
         <v>5.665</v>
       </c>
       <c r="M58">
-        <v>2.549299536</v>
+        <v>2.594822742</v>
       </c>
       <c r="N58">
-        <v>3.115700464</v>
+        <v>3.070177258</v>
       </c>
       <c r="O58">
-        <v>0.7789251159999999</v>
+        <v>0.7675443144999999</v>
       </c>
       <c r="P58">
-        <v>2.336775348</v>
+        <v>2.3026329435</v>
       </c>
       <c r="Q58">
-        <v>2.341775348</v>
+        <v>2.3076329435</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2339439279972116</v>
+        <v>0.2377597188570793</v>
       </c>
       <c r="T58">
-        <v>1.150664842586489</v>
+        <v>1.174001744477778</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.222179041733447</v>
+        <v>2.183193444510052</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1346411791085441</v>
+        <v>0.1345110298983151</v>
       </c>
       <c r="C59">
-        <v>30.79305268706649</v>
+        <v>30.28584329434055</v>
       </c>
       <c r="D59">
-        <v>63.6355426870665</v>
+        <v>63.72890329434055</v>
       </c>
       <c r="E59">
-        <v>34.07549</v>
+        <v>34.67606000000001</v>
       </c>
       <c r="F59">
-        <v>34.23249</v>
+        <v>34.83306</v>
       </c>
       <c r="G59">
         <v>1.39</v>
@@ -6125,28 +6125,28 @@
         <v>5.665</v>
       </c>
       <c r="M59">
-        <v>2.594822742</v>
+        <v>2.640345948000001</v>
       </c>
       <c r="N59">
-        <v>3.070177258</v>
+        <v>3.024654051999999</v>
       </c>
       <c r="O59">
-        <v>0.7675443144999999</v>
+        <v>0.7561635129999998</v>
       </c>
       <c r="P59">
-        <v>2.3026329435</v>
+        <v>2.268490539</v>
       </c>
       <c r="Q59">
-        <v>2.3076329435</v>
+        <v>2.273490539</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2377597188570793</v>
+        <v>0.2417572140436074</v>
       </c>
       <c r="T59">
-        <v>1.174001744477778</v>
+        <v>1.19844992741151</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.183193444510052</v>
+        <v>2.145552178225396</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1345110298983151</v>
+        <v>0.1343808806880861</v>
       </c>
       <c r="C60">
-        <v>30.28584329434059</v>
+        <v>29.77890824545067</v>
       </c>
       <c r="D60">
-        <v>63.72890329434058</v>
+        <v>63.82253824545066</v>
       </c>
       <c r="E60">
-        <v>34.67606</v>
+        <v>35.27663</v>
       </c>
       <c r="F60">
-        <v>34.83306</v>
+        <v>35.43362999999999</v>
       </c>
       <c r="G60">
         <v>1.39</v>
@@ -6207,28 +6207,28 @@
         <v>5.665</v>
       </c>
       <c r="M60">
-        <v>2.640345948</v>
+        <v>2.685869154</v>
       </c>
       <c r="N60">
-        <v>3.024654052</v>
+        <v>2.979130846</v>
       </c>
       <c r="O60">
-        <v>0.7561635130000001</v>
+        <v>0.7447827115000001</v>
       </c>
       <c r="P60">
-        <v>2.268490539</v>
+        <v>2.2343481345</v>
       </c>
       <c r="Q60">
-        <v>2.273490539</v>
+        <v>2.2393481345</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2417572140436073</v>
+        <v>0.2459497089953319</v>
       </c>
       <c r="T60">
-        <v>1.198449927411509</v>
+        <v>1.224090704634691</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.145552178225397</v>
+        <v>2.109186887069034</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1343808806880861</v>
+        <v>0.1342507314778571</v>
       </c>
       <c r="C61">
-        <v>29.77890824545067</v>
+        <v>29.27224875143142</v>
       </c>
       <c r="D61">
-        <v>63.82253824545066</v>
+        <v>63.91644875143142</v>
       </c>
       <c r="E61">
-        <v>35.27663</v>
+        <v>35.8772</v>
       </c>
       <c r="F61">
-        <v>35.43362999999999</v>
+        <v>36.0342</v>
       </c>
       <c r="G61">
         <v>1.39</v>
@@ -6289,28 +6289,28 @@
         <v>5.665</v>
       </c>
       <c r="M61">
-        <v>2.685869154</v>
+        <v>2.73139236</v>
       </c>
       <c r="N61">
-        <v>2.979130846</v>
+        <v>2.93360764</v>
       </c>
       <c r="O61">
-        <v>0.7447827115000001</v>
+        <v>0.73340191</v>
       </c>
       <c r="P61">
-        <v>2.2343481345</v>
+        <v>2.20020573</v>
       </c>
       <c r="Q61">
-        <v>2.2393481345</v>
+        <v>2.20520573</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2459497089953319</v>
+        <v>0.2503518286946428</v>
       </c>
       <c r="T61">
-        <v>1.224090704634691</v>
+        <v>1.251013520719032</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.109186887069034</v>
+        <v>2.07403377228455</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1342507314778571</v>
+        <v>0.1341205822676281</v>
       </c>
       <c r="C62">
-        <v>29.27224875143142</v>
+        <v>28.76586603045586</v>
       </c>
       <c r="D62">
-        <v>63.91644875143142</v>
+        <v>64.01063603045586</v>
       </c>
       <c r="E62">
-        <v>35.8772</v>
+        <v>36.47777</v>
       </c>
       <c r="F62">
-        <v>36.0342</v>
+        <v>36.63477</v>
       </c>
       <c r="G62">
         <v>1.39</v>
@@ -6371,28 +6371,28 @@
         <v>5.665</v>
       </c>
       <c r="M62">
-        <v>2.73139236</v>
+        <v>2.776915566</v>
       </c>
       <c r="N62">
-        <v>2.93360764</v>
+        <v>2.888084434</v>
       </c>
       <c r="O62">
-        <v>0.73340191</v>
+        <v>0.7220211085</v>
       </c>
       <c r="P62">
-        <v>2.20020573</v>
+        <v>2.1660633255</v>
       </c>
       <c r="Q62">
-        <v>2.20520573</v>
+        <v>2.1710633255</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2503518286946428</v>
+        <v>0.2549796981221234</v>
       </c>
       <c r="T62">
-        <v>1.251013520719032</v>
+        <v>1.279316994038467</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.07403377228455</v>
+        <v>2.040033218640541</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1341205822676281</v>
+        <v>0.1339904330573991</v>
       </c>
       <c r="C63">
-        <v>28.76586603045586</v>
+        <v>28.25976130788791</v>
       </c>
       <c r="D63">
-        <v>64.01063603045586</v>
+        <v>64.10510130788791</v>
       </c>
       <c r="E63">
-        <v>36.47777</v>
+        <v>37.07834</v>
       </c>
       <c r="F63">
-        <v>36.63477</v>
+        <v>37.23533999999999</v>
       </c>
       <c r="G63">
         <v>1.39</v>
@@ -6453,28 +6453,28 @@
         <v>5.665</v>
       </c>
       <c r="M63">
-        <v>2.776915566</v>
+        <v>2.822438772</v>
       </c>
       <c r="N63">
-        <v>2.888084434</v>
+        <v>2.842561228</v>
       </c>
       <c r="O63">
-        <v>0.7220211085</v>
+        <v>0.710640307</v>
       </c>
       <c r="P63">
-        <v>2.1660633255</v>
+        <v>2.131920921</v>
       </c>
       <c r="Q63">
-        <v>2.1710633255</v>
+        <v>2.136920921</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2549796981221234</v>
+        <v>0.2598511396247346</v>
       </c>
       <c r="T63">
-        <v>1.279316994038467</v>
+        <v>1.309110123848399</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.040033218640541</v>
+        <v>2.007129457049565</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1339904330573991</v>
+        <v>0.1405697838471701</v>
       </c>
       <c r="C64">
-        <v>28.25976130788791</v>
+        <v>23.20872269018411</v>
       </c>
       <c r="D64">
-        <v>64.10510130788791</v>
+        <v>59.65463269018411</v>
       </c>
       <c r="E64">
-        <v>37.07834</v>
+        <v>37.67891</v>
       </c>
       <c r="F64">
-        <v>37.23533999999999</v>
+        <v>37.83591</v>
       </c>
       <c r="G64">
         <v>1.39</v>
@@ -6535,45 +6535,45 @@
         <v>5.665</v>
       </c>
       <c r="M64">
-        <v>2.822438772</v>
+        <v>3.4052319</v>
       </c>
       <c r="N64">
-        <v>2.842561228</v>
+        <v>2.259768100000001</v>
       </c>
       <c r="O64">
-        <v>0.710640307</v>
+        <v>0.5649420250000001</v>
       </c>
       <c r="P64">
-        <v>2.131920921</v>
+        <v>1.694826075</v>
       </c>
       <c r="Q64">
-        <v>2.136920921</v>
+        <v>1.699826075</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2598511396247346</v>
+        <v>0.264985902289649</v>
       </c>
       <c r="T64">
-        <v>1.309110123848399</v>
+        <v>1.340513693107516</v>
       </c>
       <c r="U64">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V64">
         <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.007129457049565</v>
+        <v>1.663616507292793</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1405697838471701</v>
+        <v>0.1405461346369412</v>
       </c>
       <c r="C65">
-        <v>23.20872269018411</v>
+        <v>22.62304284855341</v>
       </c>
       <c r="D65">
-        <v>59.65463269018411</v>
+        <v>59.66952284855341</v>
       </c>
       <c r="E65">
-        <v>37.67891</v>
+        <v>38.27948</v>
       </c>
       <c r="F65">
-        <v>37.83591</v>
+        <v>38.43648</v>
       </c>
       <c r="G65">
         <v>1.39</v>
@@ -6617,28 +6617,28 @@
         <v>5.665</v>
       </c>
       <c r="M65">
-        <v>3.4052319</v>
+        <v>3.459283199999999</v>
       </c>
       <c r="N65">
-        <v>2.259768100000001</v>
+        <v>2.205716800000001</v>
       </c>
       <c r="O65">
-        <v>0.5649420250000001</v>
+        <v>0.5514292000000002</v>
       </c>
       <c r="P65">
-        <v>1.694826075</v>
+        <v>1.6542876</v>
       </c>
       <c r="Q65">
-        <v>1.699826075</v>
+        <v>1.6592876</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.264985902289649</v>
+        <v>0.2704059295470587</v>
       </c>
       <c r="T65">
-        <v>1.340513693107516</v>
+        <v>1.373661905103251</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.663616507292793</v>
+        <v>1.637622499366343</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1405461346369412</v>
+        <v>0.1405224854267122</v>
       </c>
       <c r="C66">
-        <v>22.62304284855341</v>
+        <v>22.03737044212638</v>
       </c>
       <c r="D66">
-        <v>59.66952284855341</v>
+        <v>59.68442044212638</v>
       </c>
       <c r="E66">
-        <v>38.27948</v>
+        <v>38.88005</v>
       </c>
       <c r="F66">
-        <v>38.43648</v>
+        <v>39.03705</v>
       </c>
       <c r="G66">
         <v>1.39</v>
@@ -6699,28 +6699,28 @@
         <v>5.665</v>
       </c>
       <c r="M66">
-        <v>3.459283199999999</v>
+        <v>3.5133345</v>
       </c>
       <c r="N66">
-        <v>2.205716800000001</v>
+        <v>2.1516655</v>
       </c>
       <c r="O66">
-        <v>0.5514292000000002</v>
+        <v>0.537916375</v>
       </c>
       <c r="P66">
-        <v>1.6542876</v>
+        <v>1.613749125</v>
       </c>
       <c r="Q66">
-        <v>1.6592876</v>
+        <v>1.618749125</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2704059295470587</v>
+        <v>0.2761356726477491</v>
       </c>
       <c r="T66">
-        <v>1.373661905103251</v>
+        <v>1.408704300641599</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.637622499366343</v>
+        <v>1.612428307068399</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1405224854267122</v>
+        <v>0.1404988362164832</v>
       </c>
       <c r="C67">
-        <v>22.03737044212638</v>
+        <v>21.45170547647342</v>
       </c>
       <c r="D67">
-        <v>59.68442044212638</v>
+        <v>59.69932547647342</v>
       </c>
       <c r="E67">
-        <v>38.88005</v>
+        <v>39.48062</v>
       </c>
       <c r="F67">
-        <v>39.03705</v>
+        <v>39.63762</v>
       </c>
       <c r="G67">
         <v>1.39</v>
@@ -6781,28 +6781,28 @@
         <v>5.665</v>
       </c>
       <c r="M67">
-        <v>3.5133345</v>
+        <v>3.5673858</v>
       </c>
       <c r="N67">
-        <v>2.1516655</v>
+        <v>2.0976142</v>
       </c>
       <c r="O67">
-        <v>0.537916375</v>
+        <v>0.5244035500000001</v>
       </c>
       <c r="P67">
-        <v>1.613749125</v>
+        <v>1.57321065</v>
       </c>
       <c r="Q67">
-        <v>1.618749125</v>
+        <v>1.57821065</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2761356726477491</v>
+        <v>0.2822024594602446</v>
       </c>
       <c r="T67">
-        <v>1.408704300641599</v>
+        <v>1.445808013564556</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.612428307068399</v>
+        <v>1.58799757514312</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1404988362164832</v>
+        <v>0.1404751870062542</v>
       </c>
       <c r="C68">
-        <v>21.45170547647342</v>
+        <v>20.86604795717051</v>
       </c>
       <c r="D68">
-        <v>59.69932547647342</v>
+        <v>59.7142379571705</v>
       </c>
       <c r="E68">
-        <v>39.48062</v>
+        <v>40.08119</v>
       </c>
       <c r="F68">
-        <v>39.63762</v>
+        <v>40.23819</v>
       </c>
       <c r="G68">
         <v>1.39</v>
@@ -6863,28 +6863,28 @@
         <v>5.665</v>
       </c>
       <c r="M68">
-        <v>3.5673858</v>
+        <v>3.6214371</v>
       </c>
       <c r="N68">
-        <v>2.0976142</v>
+        <v>2.0435629</v>
       </c>
       <c r="O68">
-        <v>0.5244035500000001</v>
+        <v>0.5108907250000001</v>
       </c>
       <c r="P68">
-        <v>1.57321065</v>
+        <v>1.532672175</v>
       </c>
       <c r="Q68">
-        <v>1.57821065</v>
+        <v>1.537672175</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2822024594602446</v>
+        <v>0.2886369303219823</v>
       </c>
       <c r="T68">
-        <v>1.445808013564556</v>
+        <v>1.485160436361632</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.58799757514312</v>
+        <v>1.564296118797701</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1404751870062542</v>
+        <v>0.1404515377960252</v>
       </c>
       <c r="C69">
-        <v>20.86604795717051</v>
+        <v>20.28039788979911</v>
       </c>
       <c r="D69">
-        <v>59.7142379571705</v>
+        <v>59.72915788979911</v>
       </c>
       <c r="E69">
-        <v>40.08119</v>
+        <v>40.68176</v>
       </c>
       <c r="F69">
-        <v>40.23819</v>
+        <v>40.83876</v>
       </c>
       <c r="G69">
         <v>1.39</v>
@@ -6945,28 +6945,28 @@
         <v>5.665</v>
       </c>
       <c r="M69">
-        <v>3.6214371</v>
+        <v>3.6754884</v>
       </c>
       <c r="N69">
-        <v>2.0435629</v>
+        <v>1.9895116</v>
       </c>
       <c r="O69">
-        <v>0.5108907250000001</v>
+        <v>0.4973779</v>
       </c>
       <c r="P69">
-        <v>1.532672175</v>
+        <v>1.4921337</v>
       </c>
       <c r="Q69">
-        <v>1.537672175</v>
+        <v>1.4971337</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2886369303219823</v>
+        <v>0.2954735556125788</v>
       </c>
       <c r="T69">
-        <v>1.485160436361632</v>
+        <v>1.526972385583525</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.564296118797701</v>
+        <v>1.541291764109499</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1404515377960252</v>
+        <v>0.1404278885857962</v>
       </c>
       <c r="C70">
-        <v>20.28039788979911</v>
+        <v>19.69475527994645</v>
       </c>
       <c r="D70">
-        <v>59.72915788979911</v>
+        <v>59.74408527994645</v>
       </c>
       <c r="E70">
-        <v>40.68176</v>
+        <v>41.28233</v>
       </c>
       <c r="F70">
-        <v>40.83876</v>
+        <v>41.43933</v>
       </c>
       <c r="G70">
         <v>1.39</v>
@@ -7027,28 +7027,28 @@
         <v>5.665</v>
       </c>
       <c r="M70">
-        <v>3.6754884</v>
+        <v>3.7295397</v>
       </c>
       <c r="N70">
-        <v>1.9895116</v>
+        <v>1.9354603</v>
       </c>
       <c r="O70">
-        <v>0.4973779</v>
+        <v>0.4838650750000001</v>
       </c>
       <c r="P70">
-        <v>1.4921337</v>
+        <v>1.451595225</v>
       </c>
       <c r="Q70">
-        <v>1.4971337</v>
+        <v>1.456595225</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2954735556125788</v>
+        <v>0.3027512535025684</v>
       </c>
       <c r="T70">
-        <v>1.526972385583525</v>
+        <v>1.571481879916507</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.541291764109499</v>
+        <v>1.518954202310811</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1404278885857962</v>
+        <v>0.1737148877295752</v>
       </c>
       <c r="C71">
-        <v>19.69475527994645</v>
+        <v>3.547118391503012</v>
       </c>
       <c r="D71">
-        <v>59.74408527994645</v>
+        <v>44.19701839150301</v>
       </c>
       <c r="E71">
-        <v>41.28233</v>
+        <v>41.88290000000001</v>
       </c>
       <c r="F71">
-        <v>41.43933</v>
+        <v>42.0399</v>
       </c>
       <c r="G71">
         <v>1.39</v>
@@ -7109,45 +7109,45 @@
         <v>5.665</v>
       </c>
       <c r="M71">
-        <v>3.7295397</v>
+        <v>6.171457320000001</v>
       </c>
       <c r="N71">
-        <v>1.9354603</v>
+        <v>-0.5064573200000009</v>
       </c>
       <c r="O71">
-        <v>0.4838650750000001</v>
+        <v>-0.1266143300000002</v>
       </c>
       <c r="P71">
-        <v>1.451595225</v>
+        <v>-0.3798429900000007</v>
       </c>
       <c r="Q71">
-        <v>1.456595225</v>
+        <v>-0.3748429900000007</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3027512535025684</v>
+        <v>0.3151221724015018</v>
       </c>
       <c r="T71">
-        <v>1.571481879916507</v>
+        <v>1.647140879911991</v>
       </c>
       <c r="U71">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.25</v>
+        <v>0.2294838846912741</v>
       </c>
       <c r="W71">
-        <v>0.0675</v>
+        <v>0.113111765727321</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.518954202310811</v>
+        <v>0.9179355387650966</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1737148877295752</v>
+        <v>0.1747248877295752</v>
       </c>
       <c r="C72">
-        <v>3.547118391503012</v>
+        <v>2.600308116552768</v>
       </c>
       <c r="D72">
-        <v>44.19701839150301</v>
+        <v>43.85077811655277</v>
       </c>
       <c r="E72">
-        <v>41.88290000000001</v>
+        <v>42.48347</v>
       </c>
       <c r="F72">
-        <v>42.0399</v>
+        <v>42.64047</v>
       </c>
       <c r="G72">
         <v>1.39</v>
@@ -7191,37 +7191,37 @@
         <v>5.665</v>
       </c>
       <c r="M72">
-        <v>6.171457320000001</v>
+        <v>6.259620996000001</v>
       </c>
       <c r="N72">
-        <v>-0.5064573200000009</v>
+        <v>-0.5946209960000006</v>
       </c>
       <c r="O72">
-        <v>-0.1266143300000002</v>
+        <v>-0.1486552490000002</v>
       </c>
       <c r="P72">
-        <v>-0.3798429900000007</v>
+        <v>-0.4459657470000005</v>
       </c>
       <c r="Q72">
-        <v>-0.3748429900000007</v>
+        <v>-0.4409657470000005</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3151221724015018</v>
+        <v>0.3244091438636225</v>
       </c>
       <c r="T72">
-        <v>1.647140879911991</v>
+        <v>1.703938841288267</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2294838846912741</v>
+        <v>0.2262517173012562</v>
       </c>
       <c r="W72">
-        <v>0.113111765727321</v>
+        <v>0.1135862479001756</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.9179355387650966</v>
+        <v>0.9050068692050248</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1747248877295752</v>
+        <v>0.1757348877295752</v>
       </c>
       <c r="C73">
-        <v>2.600308116552775</v>
+        <v>1.658880578815136</v>
       </c>
       <c r="D73">
-        <v>43.85077811655277</v>
+        <v>43.50992057881513</v>
       </c>
       <c r="E73">
-        <v>42.48347</v>
+        <v>43.08404</v>
       </c>
       <c r="F73">
-        <v>42.64046999999999</v>
+        <v>43.24104</v>
       </c>
       <c r="G73">
         <v>1.39</v>
@@ -7273,37 +7273,37 @@
         <v>5.665</v>
       </c>
       <c r="M73">
-        <v>6.259620996</v>
+        <v>6.347784672</v>
       </c>
       <c r="N73">
-        <v>-0.5946209959999997</v>
+        <v>-0.6827846720000004</v>
       </c>
       <c r="O73">
-        <v>-0.1486552489999999</v>
+        <v>-0.1706961680000001</v>
       </c>
       <c r="P73">
-        <v>-0.4459657469999998</v>
+        <v>-0.5120885040000003</v>
       </c>
       <c r="Q73">
-        <v>-0.4409657469999998</v>
+        <v>-0.5070885040000003</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3244091438636224</v>
+        <v>0.3343594704301804</v>
       </c>
       <c r="T73">
-        <v>1.703938841288266</v>
+        <v>1.764793799905704</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2262517173012562</v>
+        <v>0.2231093323387388</v>
       </c>
       <c r="W73">
-        <v>0.1135862479001756</v>
+        <v>0.1140475500126732</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.905006869205025</v>
+        <v>0.8924373293549551</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1757348877295752</v>
+        <v>0.1767448877295752</v>
       </c>
       <c r="C74">
-        <v>1.658880578815136</v>
+        <v>0.7227112244107303</v>
       </c>
       <c r="D74">
-        <v>43.50992057881513</v>
+        <v>43.17432122441073</v>
       </c>
       <c r="E74">
-        <v>43.08404</v>
+        <v>43.68461</v>
       </c>
       <c r="F74">
-        <v>43.24104</v>
+        <v>43.84161</v>
       </c>
       <c r="G74">
         <v>1.39</v>
@@ -7355,37 +7355,37 @@
         <v>5.665</v>
       </c>
       <c r="M74">
-        <v>6.347784672</v>
+        <v>6.435948348</v>
       </c>
       <c r="N74">
-        <v>-0.6827846720000004</v>
+        <v>-0.7709483480000001</v>
       </c>
       <c r="O74">
-        <v>-0.1706961680000001</v>
+        <v>-0.192737087</v>
       </c>
       <c r="P74">
-        <v>-0.5120885040000003</v>
+        <v>-0.5782112610000001</v>
       </c>
       <c r="Q74">
-        <v>-0.5070885040000003</v>
+        <v>-0.5732112610000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3343594704301804</v>
+        <v>0.3450468582238908</v>
       </c>
       <c r="T74">
-        <v>1.764793799905704</v>
+        <v>1.830156533235545</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2231093323387388</v>
+        <v>0.2200530401149204</v>
       </c>
       <c r="W74">
-        <v>0.1140475500126732</v>
+        <v>0.1144962137111297</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8924373293549551</v>
+        <v>0.8802121604596818</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1767448877295752</v>
+        <v>0.1777548877295752</v>
       </c>
       <c r="C75">
-        <v>0.7227112244107303</v>
+        <v>-0.2083206871330034</v>
       </c>
       <c r="D75">
-        <v>43.17432122441073</v>
+        <v>42.84385931286699</v>
       </c>
       <c r="E75">
-        <v>43.68461</v>
+        <v>44.28518</v>
       </c>
       <c r="F75">
-        <v>43.84161</v>
+        <v>44.44217999999999</v>
       </c>
       <c r="G75">
         <v>1.39</v>
@@ -7437,37 +7437,37 @@
         <v>5.665</v>
       </c>
       <c r="M75">
-        <v>6.435948348</v>
+        <v>6.524112024</v>
       </c>
       <c r="N75">
-        <v>-0.7709483480000001</v>
+        <v>-0.8591120239999999</v>
       </c>
       <c r="O75">
-        <v>-0.192737087</v>
+        <v>-0.214778006</v>
       </c>
       <c r="P75">
-        <v>-0.5782112610000001</v>
+        <v>-0.6443340179999999</v>
       </c>
       <c r="Q75">
-        <v>-0.5732112610000001</v>
+        <v>-0.6393340179999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3450468582238908</v>
+        <v>0.3565563527709635</v>
       </c>
       <c r="T75">
-        <v>1.830156533235545</v>
+        <v>1.90054716912922</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2200530401149204</v>
+        <v>0.2170793503836377</v>
       </c>
       <c r="W75">
-        <v>0.1144962137111297</v>
+        <v>0.114932751363682</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8802121604596818</v>
+        <v>0.8683174015345509</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1777548877295752</v>
+        <v>0.1787648877295752</v>
       </c>
       <c r="C76">
-        <v>-0.2083206871330034</v>
+        <v>-1.134332227714779</v>
       </c>
       <c r="D76">
-        <v>42.84385931286699</v>
+        <v>42.51841777228522</v>
       </c>
       <c r="E76">
-        <v>44.28518</v>
+        <v>44.88575</v>
       </c>
       <c r="F76">
-        <v>44.44217999999999</v>
+        <v>45.04275</v>
       </c>
       <c r="G76">
         <v>1.39</v>
@@ -7519,37 +7519,37 @@
         <v>5.665</v>
       </c>
       <c r="M76">
-        <v>6.524112024</v>
+        <v>6.612275700000001</v>
       </c>
       <c r="N76">
-        <v>-0.8591120239999999</v>
+        <v>-0.9472757000000005</v>
       </c>
       <c r="O76">
-        <v>-0.214778006</v>
+        <v>-0.2368189250000001</v>
       </c>
       <c r="P76">
-        <v>-0.6443340179999999</v>
+        <v>-0.7104567750000004</v>
       </c>
       <c r="Q76">
-        <v>-0.6393340179999999</v>
+        <v>-0.7054567750000004</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3565563527709635</v>
+        <v>0.3689866068818021</v>
       </c>
       <c r="T76">
-        <v>1.90054716912922</v>
+        <v>1.976569055894389</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2170793503836377</v>
+        <v>0.2141849590451892</v>
       </c>
       <c r="W76">
-        <v>0.114932751363682</v>
+        <v>0.1153576480121662</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8683174015345509</v>
+        <v>0.8567398361807569</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1787648877295752</v>
+        <v>0.1797748877295752</v>
       </c>
       <c r="C77">
-        <v>-1.134332227714779</v>
+        <v>-2.05543693894132</v>
       </c>
       <c r="D77">
-        <v>42.51841777228522</v>
+        <v>42.19788306105868</v>
       </c>
       <c r="E77">
-        <v>44.88575</v>
+        <v>45.48632</v>
       </c>
       <c r="F77">
-        <v>45.04275</v>
+        <v>45.64332</v>
       </c>
       <c r="G77">
         <v>1.39</v>
@@ -7601,37 +7601,37 @@
         <v>5.665</v>
       </c>
       <c r="M77">
-        <v>6.612275700000001</v>
+        <v>6.700439376</v>
       </c>
       <c r="N77">
-        <v>-0.9472757000000005</v>
+        <v>-1.035439376</v>
       </c>
       <c r="O77">
-        <v>-0.2368189250000001</v>
+        <v>-0.2588598440000001</v>
       </c>
       <c r="P77">
-        <v>-0.7104567750000004</v>
+        <v>-0.7765795320000002</v>
       </c>
       <c r="Q77">
-        <v>-0.7054567750000004</v>
+        <v>-0.7715795320000002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3689866068818021</v>
+        <v>0.3824527155018771</v>
       </c>
       <c r="T77">
-        <v>1.976569055894389</v>
+        <v>2.058926099889989</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2141849590451892</v>
+        <v>0.2113667358998578</v>
       </c>
       <c r="W77">
-        <v>0.1153576480121662</v>
+        <v>0.1157713631699009</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8567398361807569</v>
+        <v>0.8454669435994312</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1797748877295752</v>
+        <v>0.1807848877295752</v>
       </c>
       <c r="C78">
-        <v>-2.05543693894132</v>
+        <v>-2.971744964201257</v>
       </c>
       <c r="D78">
-        <v>42.19788306105868</v>
+        <v>41.88214503579874</v>
       </c>
       <c r="E78">
-        <v>45.48632</v>
+        <v>46.08689</v>
       </c>
       <c r="F78">
-        <v>45.64332</v>
+        <v>46.24389</v>
       </c>
       <c r="G78">
         <v>1.39</v>
@@ -7683,37 +7683,37 @@
         <v>5.665</v>
       </c>
       <c r="M78">
-        <v>6.700439376</v>
+        <v>6.788603052000001</v>
       </c>
       <c r="N78">
-        <v>-1.035439376</v>
+        <v>-1.123603052000001</v>
       </c>
       <c r="O78">
-        <v>-0.2588598440000001</v>
+        <v>-0.2809007630000002</v>
       </c>
       <c r="P78">
-        <v>-0.7765795320000002</v>
+        <v>-0.8427022890000007</v>
       </c>
       <c r="Q78">
-        <v>-0.7715795320000002</v>
+        <v>-0.8377022890000007</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3824527155018771</v>
+        <v>0.3970897900889153</v>
       </c>
       <c r="T78">
-        <v>2.058926099889989</v>
+        <v>2.148444625972162</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2113667358998578</v>
+        <v>0.2086217133557038</v>
       </c>
       <c r="W78">
-        <v>0.1157713631699009</v>
+        <v>0.1161743324793827</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8454669435994312</v>
+        <v>0.8344868534228151</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1807848877295752</v>
+        <v>0.1817948877295752</v>
       </c>
       <c r="C79">
-        <v>-2.971744964201257</v>
+        <v>-3.883363174853642</v>
       </c>
       <c r="D79">
-        <v>41.88214503579874</v>
+        <v>41.57109682514636</v>
       </c>
       <c r="E79">
-        <v>46.08689</v>
+        <v>46.68746</v>
       </c>
       <c r="F79">
-        <v>46.24389</v>
+        <v>46.84446</v>
       </c>
       <c r="G79">
         <v>1.39</v>
@@ -7765,37 +7765,37 @@
         <v>5.665</v>
       </c>
       <c r="M79">
-        <v>6.788603052000001</v>
+        <v>6.876766728000001</v>
       </c>
       <c r="N79">
-        <v>-1.123603052000001</v>
+        <v>-1.211766728000001</v>
       </c>
       <c r="O79">
-        <v>-0.2809007630000002</v>
+        <v>-0.3029416820000002</v>
       </c>
       <c r="P79">
-        <v>-0.8427022890000007</v>
+        <v>-0.9088250460000005</v>
       </c>
       <c r="Q79">
-        <v>-0.8377022890000007</v>
+        <v>-0.9038250460000005</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3970897900889153</v>
+        <v>0.4130575078202296</v>
       </c>
       <c r="T79">
-        <v>2.148444625972162</v>
+        <v>2.246101199879988</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2086217133557038</v>
+        <v>0.2059470760049896</v>
       </c>
       <c r="W79">
-        <v>0.1161743324793827</v>
+        <v>0.1165669692424675</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8344868534228151</v>
+        <v>0.8237883040199585</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1817948877295752</v>
+        <v>0.1828048877295751</v>
       </c>
       <c r="C80">
-        <v>-3.883363174853642</v>
+        <v>-4.790395290835015</v>
       </c>
       <c r="D80">
-        <v>41.57109682514636</v>
+        <v>41.26463470916498</v>
       </c>
       <c r="E80">
-        <v>46.68746</v>
+        <v>47.28803</v>
       </c>
       <c r="F80">
-        <v>46.84446</v>
+        <v>47.44503</v>
       </c>
       <c r="G80">
         <v>1.39</v>
@@ -7847,37 +7847,37 @@
         <v>5.665</v>
       </c>
       <c r="M80">
-        <v>6.876766728000001</v>
+        <v>6.964930404</v>
       </c>
       <c r="N80">
-        <v>-1.211766728000001</v>
+        <v>-1.299930404</v>
       </c>
       <c r="O80">
-        <v>-0.3029416820000002</v>
+        <v>-0.3249826010000001</v>
       </c>
       <c r="P80">
-        <v>-0.9088250460000005</v>
+        <v>-0.9749478030000003</v>
       </c>
       <c r="Q80">
-        <v>-0.9038250460000005</v>
+        <v>-0.9699478030000003</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4130575078202296</v>
+        <v>0.4305459605735739</v>
       </c>
       <c r="T80">
-        <v>2.246101199879988</v>
+        <v>2.353058399874273</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2059470760049896</v>
+        <v>0.2033401509922683</v>
       </c>
       <c r="W80">
-        <v>0.1165669692424675</v>
+        <v>0.116949665834335</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8237883040199585</v>
+        <v>0.8133606039690731</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1828048877295751</v>
+        <v>0.1838148877295752</v>
       </c>
       <c r="C81">
-        <v>-4.790395290835015</v>
+        <v>-5.692941995970777</v>
       </c>
       <c r="D81">
-        <v>41.26463470916498</v>
+        <v>40.96265800402922</v>
       </c>
       <c r="E81">
-        <v>47.28803</v>
+        <v>47.8886</v>
       </c>
       <c r="F81">
-        <v>47.44503</v>
+        <v>48.0456</v>
       </c>
       <c r="G81">
         <v>1.39</v>
@@ -7929,37 +7929,37 @@
         <v>5.665</v>
       </c>
       <c r="M81">
-        <v>6.964930404</v>
+        <v>7.053094080000001</v>
       </c>
       <c r="N81">
-        <v>-1.299930404</v>
+        <v>-1.388094080000001</v>
       </c>
       <c r="O81">
-        <v>-0.3249826010000001</v>
+        <v>-0.3470235200000003</v>
       </c>
       <c r="P81">
-        <v>-0.9749478030000003</v>
+        <v>-1.041070560000001</v>
       </c>
       <c r="Q81">
-        <v>-0.9699478030000003</v>
+        <v>-1.036070560000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4305459605735739</v>
+        <v>0.4497832586022527</v>
       </c>
       <c r="T81">
-        <v>2.353058399874273</v>
+        <v>2.470711319867987</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2033401509922683</v>
+        <v>0.2007983991048649</v>
       </c>
       <c r="W81">
-        <v>0.116949665834335</v>
+        <v>0.1173227950114059</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8133606039690731</v>
+        <v>0.8031935964194595</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1838148877295752</v>
+        <v>0.232723272928987</v>
       </c>
       <c r="C82">
-        <v>-5.692941995970777</v>
+        <v>-17.01137192352478</v>
       </c>
       <c r="D82">
-        <v>40.96265800402922</v>
+        <v>30.24479807647522</v>
       </c>
       <c r="E82">
-        <v>47.8886</v>
+        <v>48.48917</v>
       </c>
       <c r="F82">
-        <v>48.0456</v>
+        <v>48.64617</v>
       </c>
       <c r="G82">
         <v>1.39</v>
@@ -8011,45 +8011,45 @@
         <v>5.665</v>
       </c>
       <c r="M82">
-        <v>7.053094080000001</v>
+        <v>9.768150936</v>
       </c>
       <c r="N82">
-        <v>-1.388094080000001</v>
+        <v>-4.103150936</v>
       </c>
       <c r="O82">
-        <v>-0.3470235200000003</v>
+        <v>-1.025787734</v>
       </c>
       <c r="P82">
-        <v>-1.041070560000001</v>
+        <v>-3.077363202</v>
       </c>
       <c r="Q82">
-        <v>-1.036070560000001</v>
+        <v>-3.072363202</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4497832586022527</v>
+        <v>0.4929317732624333</v>
       </c>
       <c r="T82">
-        <v>2.470711319867987</v>
+        <v>2.734602264198826</v>
       </c>
       <c r="U82">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.2007983991048649</v>
+        <v>0.1449864983945412</v>
       </c>
       <c r="W82">
-        <v>0.1173227950114059</v>
+        <v>0.1716867111223761</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.8031935964194595</v>
+        <v>0.5799459935781648</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.232723272928987</v>
+        <v>0.2342732729289869</v>
       </c>
       <c r="C83">
-        <v>-17.01137192352478</v>
+        <v>-17.86067446947149</v>
       </c>
       <c r="D83">
-        <v>30.24479807647522</v>
+        <v>29.99606553052851</v>
       </c>
       <c r="E83">
-        <v>48.48917</v>
+        <v>49.08974000000001</v>
       </c>
       <c r="F83">
-        <v>48.64617</v>
+        <v>49.24674</v>
       </c>
       <c r="G83">
         <v>1.39</v>
@@ -8093,37 +8093,37 @@
         <v>5.665</v>
       </c>
       <c r="M83">
-        <v>9.768150936</v>
+        <v>9.888745392000001</v>
       </c>
       <c r="N83">
-        <v>-4.103150936</v>
+        <v>-4.223745392000001</v>
       </c>
       <c r="O83">
-        <v>-1.025787734</v>
+        <v>-1.055936348</v>
       </c>
       <c r="P83">
-        <v>-3.077363202</v>
+        <v>-3.167809044</v>
       </c>
       <c r="Q83">
-        <v>-3.072363202</v>
+        <v>-3.162809044</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4929317732624333</v>
+        <v>0.5177724273325685</v>
       </c>
       <c r="T83">
-        <v>2.734602264198826</v>
+        <v>2.886524612209872</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1449864983945412</v>
+        <v>0.1432183703653395</v>
       </c>
       <c r="W83">
-        <v>0.1716867111223761</v>
+        <v>0.1720417512306398</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5799459935781648</v>
+        <v>0.5728734814613579</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2342732729289869</v>
+        <v>0.235823272928987</v>
       </c>
       <c r="C84">
-        <v>-17.86067446947149</v>
+        <v>-18.70591924459598</v>
       </c>
       <c r="D84">
-        <v>29.99606553052851</v>
+        <v>29.75139075540402</v>
       </c>
       <c r="E84">
-        <v>49.08974000000001</v>
+        <v>49.69031</v>
       </c>
       <c r="F84">
-        <v>49.24674</v>
+        <v>49.84731</v>
       </c>
       <c r="G84">
         <v>1.39</v>
@@ -8175,37 +8175,37 @@
         <v>5.665</v>
       </c>
       <c r="M84">
-        <v>9.888745392000001</v>
+        <v>10.009339848</v>
       </c>
       <c r="N84">
-        <v>-4.223745392000001</v>
+        <v>-4.344339848</v>
       </c>
       <c r="O84">
-        <v>-1.055936348</v>
+        <v>-1.086084962</v>
       </c>
       <c r="P84">
-        <v>-3.167809044</v>
+        <v>-3.258254886</v>
       </c>
       <c r="Q84">
-        <v>-3.162809044</v>
+        <v>-3.253254886</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5177724273325685</v>
+        <v>0.5455355112933078</v>
       </c>
       <c r="T84">
-        <v>2.886524612209872</v>
+        <v>3.056320177633983</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1432183703653395</v>
+        <v>0.1414928478308173</v>
       </c>
       <c r="W84">
-        <v>0.1720417512306398</v>
+        <v>0.1723882361555719</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5728734814613579</v>
+        <v>0.5659713913232692</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.235823272928987</v>
+        <v>0.237373272928987</v>
       </c>
       <c r="C85">
-        <v>-18.70591924459598</v>
+        <v>-19.54720474193975</v>
       </c>
       <c r="D85">
-        <v>29.75139075540402</v>
+        <v>29.51067525806024</v>
       </c>
       <c r="E85">
-        <v>49.69031</v>
+        <v>50.29088</v>
       </c>
       <c r="F85">
-        <v>49.84731</v>
+        <v>50.44788</v>
       </c>
       <c r="G85">
         <v>1.39</v>
@@ -8257,37 +8257,37 @@
         <v>5.665</v>
       </c>
       <c r="M85">
-        <v>10.009339848</v>
+        <v>10.129934304</v>
       </c>
       <c r="N85">
-        <v>-4.344339848</v>
+        <v>-4.464934304000001</v>
       </c>
       <c r="O85">
-        <v>-1.086084962</v>
+        <v>-1.116233576</v>
       </c>
       <c r="P85">
-        <v>-3.258254886</v>
+        <v>-3.348700728000001</v>
       </c>
       <c r="Q85">
-        <v>-3.253254886</v>
+        <v>-3.343700728000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5455355112933078</v>
+        <v>0.5767689807491396</v>
       </c>
       <c r="T85">
-        <v>3.056320177633983</v>
+        <v>3.247340188736107</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1414928478308173</v>
+        <v>0.1398084091661647</v>
       </c>
       <c r="W85">
-        <v>0.1723882361555719</v>
+        <v>0.1727264714394341</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5659713913232692</v>
+        <v>0.5592336366646589</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2373732729289869</v>
+        <v>0.238923272928987</v>
       </c>
       <c r="C86">
-        <v>-19.54720474193975</v>
+        <v>-20.3846262925388</v>
       </c>
       <c r="D86">
-        <v>29.51067525806024</v>
+        <v>29.2738237074612</v>
       </c>
       <c r="E86">
-        <v>50.29087999999999</v>
+        <v>50.89145</v>
       </c>
       <c r="F86">
-        <v>50.44787999999999</v>
+        <v>51.04845</v>
       </c>
       <c r="G86">
         <v>1.39</v>
@@ -8339,37 +8339,37 @@
         <v>5.665</v>
       </c>
       <c r="M86">
-        <v>10.129934304</v>
+        <v>10.25052876</v>
       </c>
       <c r="N86">
-        <v>-4.464934303999999</v>
+        <v>-4.58552876</v>
       </c>
       <c r="O86">
-        <v>-1.116233576</v>
+        <v>-1.14638219</v>
       </c>
       <c r="P86">
-        <v>-3.348700727999999</v>
+        <v>-3.43914657</v>
       </c>
       <c r="Q86">
-        <v>-3.343700727999999</v>
+        <v>-3.43414657</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5767689807491392</v>
+        <v>0.6121669127990819</v>
       </c>
       <c r="T86">
-        <v>3.247340188736104</v>
+        <v>3.463829534651845</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1398084091661647</v>
+        <v>0.1381636043524451</v>
       </c>
       <c r="W86">
-        <v>0.1727264714394341</v>
+        <v>0.173056748246029</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5592336366646589</v>
+        <v>0.5526544174097805</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.238923272928987</v>
+        <v>0.2404732729289869</v>
       </c>
       <c r="C87">
-        <v>-20.3846262925388</v>
+        <v>-21.21827619130392</v>
       </c>
       <c r="D87">
-        <v>29.2738237074612</v>
+        <v>29.04074380869607</v>
       </c>
       <c r="E87">
-        <v>50.89145</v>
+        <v>51.49202</v>
       </c>
       <c r="F87">
-        <v>51.04845</v>
+        <v>51.64901999999999</v>
       </c>
       <c r="G87">
         <v>1.39</v>
@@ -8421,37 +8421,37 @@
         <v>5.665</v>
       </c>
       <c r="M87">
-        <v>10.25052876</v>
+        <v>10.371123216</v>
       </c>
       <c r="N87">
-        <v>-4.58552876</v>
+        <v>-4.706123215999999</v>
       </c>
       <c r="O87">
-        <v>-1.14638219</v>
+        <v>-1.176530804</v>
       </c>
       <c r="P87">
-        <v>-3.43914657</v>
+        <v>-3.529592412</v>
       </c>
       <c r="Q87">
-        <v>-3.43414657</v>
+        <v>-3.524592412</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6121669127990819</v>
+        <v>0.6526216922847305</v>
       </c>
       <c r="T87">
-        <v>3.463829534651845</v>
+        <v>3.71124592998412</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1381636043524451</v>
+        <v>0.1365570508134632</v>
       </c>
       <c r="W87">
-        <v>0.173056748246029</v>
+        <v>0.1733793441966566</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5526544174097805</v>
+        <v>0.5462282032538529</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2404732729289869</v>
+        <v>0.242023272928987</v>
       </c>
       <c r="C88">
-        <v>-21.21827619130392</v>
+        <v>-22.04824381693506</v>
       </c>
       <c r="D88">
-        <v>29.04074380869607</v>
+        <v>28.81134618306494</v>
       </c>
       <c r="E88">
-        <v>51.49202</v>
+        <v>52.09259</v>
       </c>
       <c r="F88">
-        <v>51.64901999999999</v>
+        <v>52.24959</v>
       </c>
       <c r="G88">
         <v>1.39</v>
@@ -8503,37 +8503,37 @@
         <v>5.665</v>
       </c>
       <c r="M88">
-        <v>10.371123216</v>
+        <v>10.491717672</v>
       </c>
       <c r="N88">
-        <v>-4.706123215999999</v>
+        <v>-4.826717672</v>
       </c>
       <c r="O88">
-        <v>-1.176530804</v>
+        <v>-1.206679418</v>
       </c>
       <c r="P88">
-        <v>-3.529592412</v>
+        <v>-3.620038254</v>
       </c>
       <c r="Q88">
-        <v>-3.524592412</v>
+        <v>-3.615038254</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6526216922847305</v>
+        <v>0.6993002839989406</v>
       </c>
       <c r="T88">
-        <v>3.71124592998412</v>
+        <v>3.996726386136745</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1365570508134632</v>
+        <v>0.1349874295397452</v>
       </c>
       <c r="W88">
-        <v>0.1733793441966566</v>
+        <v>0.1736945241484192</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5462282032538529</v>
+        <v>0.539949718158981</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.242023272928987</v>
+        <v>0.243573272928987</v>
       </c>
       <c r="C89">
-        <v>-22.04824381693506</v>
+        <v>-22.87461574619669</v>
       </c>
       <c r="D89">
-        <v>28.81134618306494</v>
+        <v>28.58554425380331</v>
       </c>
       <c r="E89">
-        <v>52.09259</v>
+        <v>52.69316</v>
       </c>
       <c r="F89">
-        <v>52.24959</v>
+        <v>52.85016</v>
       </c>
       <c r="G89">
         <v>1.39</v>
@@ -8585,37 +8585,37 @@
         <v>5.665</v>
       </c>
       <c r="M89">
-        <v>10.491717672</v>
+        <v>10.612312128</v>
       </c>
       <c r="N89">
-        <v>-4.826717672</v>
+        <v>-4.947312127999999</v>
       </c>
       <c r="O89">
-        <v>-1.206679418</v>
+        <v>-1.236828032</v>
       </c>
       <c r="P89">
-        <v>-3.620038254</v>
+        <v>-3.710484095999999</v>
       </c>
       <c r="Q89">
-        <v>-3.615038254</v>
+        <v>-3.705484095999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6993002839989406</v>
+        <v>0.7537586409988526</v>
       </c>
       <c r="T89">
-        <v>3.996726386136745</v>
+        <v>4.329786918314808</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1349874295397452</v>
+        <v>0.1334534814767936</v>
       </c>
       <c r="W89">
-        <v>0.1736945241484192</v>
+        <v>0.1740025409194599</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.539949718158981</v>
+        <v>0.5338139259071744</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.243573272928987</v>
+        <v>0.2451232729289869</v>
       </c>
       <c r="C90">
-        <v>-22.87461574619669</v>
+        <v>-23.69747586286148</v>
       </c>
       <c r="D90">
-        <v>28.58554425380331</v>
+        <v>28.36325413713851</v>
       </c>
       <c r="E90">
-        <v>52.69316</v>
+        <v>53.29373</v>
       </c>
       <c r="F90">
-        <v>52.85016</v>
+        <v>53.45072999999999</v>
       </c>
       <c r="G90">
         <v>1.39</v>
@@ -8667,37 +8667,37 @@
         <v>5.665</v>
       </c>
       <c r="M90">
-        <v>10.612312128</v>
+        <v>10.732906584</v>
       </c>
       <c r="N90">
-        <v>-4.947312127999999</v>
+        <v>-5.067906583999998</v>
       </c>
       <c r="O90">
-        <v>-1.236828032</v>
+        <v>-1.266976646</v>
       </c>
       <c r="P90">
-        <v>-3.710484095999999</v>
+        <v>-3.800929937999999</v>
       </c>
       <c r="Q90">
-        <v>-3.705484095999999</v>
+        <v>-3.795929937999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7537586409988526</v>
+        <v>0.8181185174532937</v>
       </c>
       <c r="T90">
-        <v>4.329786918314808</v>
+        <v>4.723403910888881</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1334534814767936</v>
+        <v>0.1319540041568296</v>
       </c>
       <c r="W90">
-        <v>0.1740025409194599</v>
+        <v>0.1743036359653086</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5338139259071744</v>
+        <v>0.5278160166273186</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2451232729289869</v>
+        <v>0.2466732729289869</v>
       </c>
       <c r="C91">
-        <v>-23.69747586286148</v>
+        <v>-24.51690546161013</v>
       </c>
       <c r="D91">
-        <v>28.36325413713851</v>
+        <v>28.14439453838987</v>
       </c>
       <c r="E91">
-        <v>53.29373</v>
+        <v>53.8943</v>
       </c>
       <c r="F91">
-        <v>53.45072999999999</v>
+        <v>54.0513</v>
       </c>
       <c r="G91">
         <v>1.39</v>
@@ -8749,37 +8749,37 @@
         <v>5.665</v>
       </c>
       <c r="M91">
-        <v>10.732906584</v>
+        <v>10.85350104</v>
       </c>
       <c r="N91">
-        <v>-5.067906583999998</v>
+        <v>-5.188501039999999</v>
       </c>
       <c r="O91">
-        <v>-1.266976646</v>
+        <v>-1.29712526</v>
       </c>
       <c r="P91">
-        <v>-3.800929937999999</v>
+        <v>-3.89137578</v>
       </c>
       <c r="Q91">
-        <v>-3.795929937999999</v>
+        <v>-3.88637578</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8181185174532937</v>
+        <v>0.8953503691986232</v>
       </c>
       <c r="T91">
-        <v>4.723403910888881</v>
+        <v>5.19574430197777</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1319540041568296</v>
+        <v>0.1304878485550871</v>
       </c>
       <c r="W91">
-        <v>0.1743036359653086</v>
+        <v>0.1745980400101385</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5278160166273186</v>
+        <v>0.5219513942203483</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2466732729289869</v>
+        <v>0.248223272928987</v>
       </c>
       <c r="C92">
-        <v>-24.51690546161013</v>
+        <v>-25.3329833471575</v>
       </c>
       <c r="D92">
-        <v>28.14439453838987</v>
+        <v>27.9288866528425</v>
       </c>
       <c r="E92">
-        <v>53.8943</v>
+        <v>54.49487</v>
       </c>
       <c r="F92">
-        <v>54.0513</v>
+        <v>54.65187</v>
       </c>
       <c r="G92">
         <v>1.39</v>
@@ -8831,37 +8831,37 @@
         <v>5.665</v>
       </c>
       <c r="M92">
-        <v>10.85350104</v>
+        <v>10.974095496</v>
       </c>
       <c r="N92">
-        <v>-5.188501039999999</v>
+        <v>-5.309095495999999</v>
       </c>
       <c r="O92">
-        <v>-1.29712526</v>
+        <v>-1.327273874</v>
       </c>
       <c r="P92">
-        <v>-3.89137578</v>
+        <v>-3.981821621999999</v>
       </c>
       <c r="Q92">
-        <v>-3.88637578</v>
+        <v>-3.976821621999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8953503691986232</v>
+        <v>0.989744854665137</v>
       </c>
       <c r="T92">
-        <v>5.19574430197777</v>
+        <v>5.773049224419744</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1304878485550871</v>
+        <v>0.1290539161533828</v>
       </c>
       <c r="W92">
-        <v>0.1745980400101385</v>
+        <v>0.1748859736364007</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5219513942203483</v>
+        <v>0.5162156646135314</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.248223272928987</v>
+        <v>0.249773272928987</v>
       </c>
       <c r="C93">
-        <v>-25.3329833471575</v>
+        <v>-26.14578592885941</v>
       </c>
       <c r="D93">
-        <v>27.9288866528425</v>
+        <v>27.71665407114059</v>
       </c>
       <c r="E93">
-        <v>54.49487</v>
+        <v>55.09544</v>
       </c>
       <c r="F93">
-        <v>54.65187</v>
+        <v>55.25244</v>
       </c>
       <c r="G93">
         <v>1.39</v>
@@ -8913,37 +8913,37 @@
         <v>5.665</v>
       </c>
       <c r="M93">
-        <v>10.974095496</v>
+        <v>11.094689952</v>
       </c>
       <c r="N93">
-        <v>-5.309095495999999</v>
+        <v>-5.429689951999999</v>
       </c>
       <c r="O93">
-        <v>-1.327273874</v>
+        <v>-1.357422488</v>
       </c>
       <c r="P93">
-        <v>-3.981821621999999</v>
+        <v>-4.072267463999999</v>
       </c>
       <c r="Q93">
-        <v>-3.976821621999999</v>
+        <v>-4.067267463999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.989744854665137</v>
+        <v>1.107737961498279</v>
       </c>
       <c r="T93">
-        <v>5.773049224419744</v>
+        <v>6.494680377472214</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1290539161533828</v>
+        <v>0.1276511561951939</v>
       </c>
       <c r="W93">
-        <v>0.1748859736364007</v>
+        <v>0.1751676478360051</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5162156646135314</v>
+        <v>0.5106046247807755</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.249773272928987</v>
+        <v>0.2513232729289869</v>
       </c>
       <c r="C94">
-        <v>-26.14578592885941</v>
+        <v>-26.95538731103825</v>
       </c>
       <c r="D94">
-        <v>27.71665407114059</v>
+        <v>27.50762268896174</v>
       </c>
       <c r="E94">
-        <v>55.09544</v>
+        <v>55.69601</v>
       </c>
       <c r="F94">
-        <v>55.25244</v>
+        <v>55.85301</v>
       </c>
       <c r="G94">
         <v>1.39</v>
@@ -8995,37 +8995,37 @@
         <v>5.665</v>
       </c>
       <c r="M94">
-        <v>11.094689952</v>
+        <v>11.215284408</v>
       </c>
       <c r="N94">
-        <v>-5.429689951999999</v>
+        <v>-5.550284408</v>
       </c>
       <c r="O94">
-        <v>-1.357422488</v>
+        <v>-1.387571102</v>
       </c>
       <c r="P94">
-        <v>-4.072267463999999</v>
+        <v>-4.162713306000001</v>
       </c>
       <c r="Q94">
-        <v>-4.067267463999999</v>
+        <v>-4.157713306000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.107737961498279</v>
+        <v>1.259443384569462</v>
       </c>
       <c r="T94">
-        <v>6.494680377472214</v>
+        <v>7.422491859968245</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1276511561951939</v>
+        <v>0.1262785631178262</v>
       </c>
       <c r="W94">
-        <v>0.1751676478360051</v>
+        <v>0.1754432645259405</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5106046247807755</v>
+        <v>0.5051142524713048</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2513232729289869</v>
+        <v>0.2874512315846727</v>
       </c>
       <c r="C95">
-        <v>-26.95538731103825</v>
+        <v>-31.66847206507458</v>
       </c>
       <c r="D95">
-        <v>27.50762268896174</v>
+        <v>23.39510793492542</v>
       </c>
       <c r="E95">
-        <v>55.69601</v>
+        <v>56.29658000000001</v>
       </c>
       <c r="F95">
-        <v>55.85301</v>
+        <v>56.45358</v>
       </c>
       <c r="G95">
         <v>1.39</v>
@@ -9077,45 +9077,45 @@
         <v>5.665</v>
       </c>
       <c r="M95">
-        <v>11.215284408</v>
+        <v>13.311754164</v>
       </c>
       <c r="N95">
-        <v>-5.550284408</v>
+        <v>-7.646754164000002</v>
       </c>
       <c r="O95">
-        <v>-1.387571102</v>
+        <v>-1.911688541</v>
       </c>
       <c r="P95">
-        <v>-4.162713306000001</v>
+        <v>-5.735065623000001</v>
       </c>
       <c r="Q95">
-        <v>-4.157713306000001</v>
+        <v>-5.730065623000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.259443384569462</v>
+        <v>1.489683259592469</v>
       </c>
       <c r="T95">
-        <v>7.422491859968245</v>
+        <v>8.830610274262261</v>
       </c>
       <c r="U95">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1262785631178262</v>
+        <v>0.1063909371035467</v>
       </c>
       <c r="W95">
-        <v>0.1754432645259405</v>
+        <v>0.2107130170309837</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.5051142524713048</v>
+        <v>0.4255637484141868</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2874512315846727</v>
+        <v>0.2893512315846727</v>
       </c>
       <c r="C96">
-        <v>-31.66847206507458</v>
+        <v>-32.45155276225783</v>
       </c>
       <c r="D96">
-        <v>23.39510793492542</v>
+        <v>23.21259723774217</v>
       </c>
       <c r="E96">
-        <v>56.29658000000001</v>
+        <v>56.89715</v>
       </c>
       <c r="F96">
-        <v>56.45358</v>
+        <v>57.05415</v>
       </c>
       <c r="G96">
         <v>1.39</v>
@@ -9159,37 +9159,37 @@
         <v>5.665</v>
       </c>
       <c r="M96">
-        <v>13.311754164</v>
+        <v>13.45336857</v>
       </c>
       <c r="N96">
-        <v>-7.646754164000002</v>
+        <v>-7.78836857</v>
       </c>
       <c r="O96">
-        <v>-1.911688541</v>
+        <v>-1.9470921425</v>
       </c>
       <c r="P96">
-        <v>-5.735065623000001</v>
+        <v>-5.8412764275</v>
       </c>
       <c r="Q96">
-        <v>-5.730065623000002</v>
+        <v>-5.836276427500001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.489683259592469</v>
+        <v>1.778459911510964</v>
       </c>
       <c r="T96">
-        <v>8.830610274262261</v>
+        <v>10.59673232911472</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1063909371035467</v>
+        <v>0.1052710325024567</v>
       </c>
       <c r="W96">
-        <v>0.2107130170309837</v>
+        <v>0.2109770905359207</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4255637484141868</v>
+        <v>0.4210841300098269</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2893512315846727</v>
+        <v>0.2912512315846727</v>
       </c>
       <c r="C97">
-        <v>-32.45155276225783</v>
+        <v>-33.23180788531452</v>
       </c>
       <c r="D97">
-        <v>23.21259723774217</v>
+        <v>23.03291211468548</v>
       </c>
       <c r="E97">
-        <v>56.89715</v>
+        <v>57.49772</v>
       </c>
       <c r="F97">
-        <v>57.05415</v>
+        <v>57.65472</v>
       </c>
       <c r="G97">
         <v>1.39</v>
@@ -9241,37 +9241,37 @@
         <v>5.665</v>
       </c>
       <c r="M97">
-        <v>13.45336857</v>
+        <v>13.594982976</v>
       </c>
       <c r="N97">
-        <v>-7.78836857</v>
+        <v>-7.929982976000001</v>
       </c>
       <c r="O97">
-        <v>-1.9470921425</v>
+        <v>-1.982495744</v>
       </c>
       <c r="P97">
-        <v>-5.8412764275</v>
+        <v>-5.947487232</v>
       </c>
       <c r="Q97">
-        <v>-5.836276427500001</v>
+        <v>-5.942487232</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.778459911510964</v>
+        <v>2.211624889388705</v>
       </c>
       <c r="T97">
-        <v>10.59673232911472</v>
+        <v>13.2459154113934</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1052710325024567</v>
+        <v>0.1041744592472228</v>
       </c>
       <c r="W97">
-        <v>0.2109770905359207</v>
+        <v>0.2112356625095049</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4210841300098269</v>
+        <v>0.4166978369888913</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2912512315846727</v>
+        <v>0.2931512315846728</v>
       </c>
       <c r="C98">
-        <v>-33.23180788531451</v>
+        <v>-34.00930254721143</v>
       </c>
       <c r="D98">
-        <v>23.03291211468548</v>
+        <v>22.85598745278856</v>
       </c>
       <c r="E98">
-        <v>57.49771999999999</v>
+        <v>58.09829</v>
       </c>
       <c r="F98">
-        <v>57.65471999999999</v>
+        <v>58.25529</v>
       </c>
       <c r="G98">
         <v>1.39</v>
@@ -9323,37 +9323,37 @@
         <v>5.665</v>
       </c>
       <c r="M98">
-        <v>13.594982976</v>
+        <v>13.736597382</v>
       </c>
       <c r="N98">
-        <v>-7.929982975999999</v>
+        <v>-8.071597382</v>
       </c>
       <c r="O98">
-        <v>-1.982495744</v>
+        <v>-2.0178993455</v>
       </c>
       <c r="P98">
-        <v>-5.947487231999999</v>
+        <v>-6.0536980365</v>
       </c>
       <c r="Q98">
-        <v>-5.942487232</v>
+        <v>-6.0486980365</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.211624889388699</v>
+        <v>2.933566519184933</v>
       </c>
       <c r="T98">
-        <v>13.24591541139337</v>
+        <v>17.66122054852449</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1041744592472228</v>
+        <v>0.1031004957498288</v>
       </c>
       <c r="W98">
-        <v>0.2112356625095049</v>
+        <v>0.2114889031021904</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4166978369888913</v>
+        <v>0.4124019829993151</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2931512315846728</v>
+        <v>0.2950512315846727</v>
       </c>
       <c r="C99">
-        <v>-34.00930254721143</v>
+        <v>-34.78409987553476</v>
       </c>
       <c r="D99">
-        <v>22.85598745278856</v>
+        <v>22.68176012446523</v>
       </c>
       <c r="E99">
-        <v>58.09829</v>
+        <v>58.69886</v>
       </c>
       <c r="F99">
-        <v>58.25529</v>
+        <v>58.85585999999999</v>
       </c>
       <c r="G99">
         <v>1.39</v>
@@ -9405,37 +9405,37 @@
         <v>5.665</v>
       </c>
       <c r="M99">
-        <v>13.736597382</v>
+        <v>13.878211788</v>
       </c>
       <c r="N99">
-        <v>-8.071597382</v>
+        <v>-8.213211787999999</v>
       </c>
       <c r="O99">
-        <v>-2.0178993455</v>
+        <v>-2.053302947</v>
       </c>
       <c r="P99">
-        <v>-6.0536980365</v>
+        <v>-6.159908840999999</v>
       </c>
       <c r="Q99">
-        <v>-6.0486980365</v>
+        <v>-6.154908840999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.933566519184933</v>
+        <v>4.377449778777398</v>
       </c>
       <c r="T99">
-        <v>17.66122054852449</v>
+        <v>26.49183082278673</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1031004957498288</v>
+        <v>0.1020484498748305</v>
       </c>
       <c r="W99">
-        <v>0.2114889031021904</v>
+        <v>0.211736975519515</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4124019829993151</v>
+        <v>0.4081937994993221</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2950512315846727</v>
+        <v>0.2969512315846727</v>
       </c>
       <c r="C100">
-        <v>-34.78409987553476</v>
+        <v>-35.55626108758884</v>
       </c>
       <c r="D100">
-        <v>22.68176012446523</v>
+        <v>22.51016891241116</v>
       </c>
       <c r="E100">
-        <v>58.69886</v>
+        <v>59.29943</v>
       </c>
       <c r="F100">
-        <v>58.85585999999999</v>
+        <v>59.45643</v>
       </c>
       <c r="G100">
         <v>1.39</v>
@@ -9487,37 +9487,37 @@
         <v>5.665</v>
       </c>
       <c r="M100">
-        <v>13.878211788</v>
+        <v>14.019826194</v>
       </c>
       <c r="N100">
-        <v>-8.213211787999999</v>
+        <v>-8.354826194000001</v>
       </c>
       <c r="O100">
-        <v>-2.053302947</v>
+        <v>-2.0887065485</v>
       </c>
       <c r="P100">
-        <v>-6.159908840999999</v>
+        <v>-6.266119645500001</v>
       </c>
       <c r="Q100">
-        <v>-6.154908840999999</v>
+        <v>-6.261119645500001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.377449778777398</v>
+        <v>8.709099557554797</v>
       </c>
       <c r="T100">
-        <v>26.49183082278673</v>
+        <v>52.98366164557347</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1020484498748305</v>
+        <v>0.1010176574518524</v>
       </c>
       <c r="W100">
-        <v>0.211736975519515</v>
+        <v>0.2119800363728532</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4081937994993221</v>
+        <v>0.4040706298074097</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2969512315846727</v>
-      </c>
-      <c r="C101">
-        <v>-35.55626108758884</v>
-      </c>
-      <c r="D101">
-        <v>22.51016891241116</v>
-      </c>
-      <c r="E101">
-        <v>59.29943</v>
-      </c>
-      <c r="F101">
-        <v>59.45643</v>
-      </c>
-      <c r="G101">
-        <v>1.39</v>
-      </c>
-      <c r="H101">
-        <v>59.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.67</v>
-      </c>
-      <c r="K101">
-        <v>0.005</v>
-      </c>
-      <c r="L101">
-        <v>5.665</v>
-      </c>
-      <c r="M101">
-        <v>14.019826194</v>
-      </c>
-      <c r="N101">
-        <v>-8.354826194000001</v>
-      </c>
-      <c r="O101">
-        <v>-2.0887065485</v>
-      </c>
-      <c r="P101">
-        <v>-6.266119645500001</v>
-      </c>
-      <c r="Q101">
-        <v>-6.261119645500001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.709099557554797</v>
-      </c>
-      <c r="T101">
-        <v>52.98366164557347</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1010176574518524</v>
-      </c>
-      <c r="W101">
-        <v>0.2119800363728532</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4040706298074097</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
